--- a/documentation/Cases.xlsx
+++ b/documentation/Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="505">
   <si>
     <t xml:space="preserve">Test Case - ID</t>
   </si>
@@ -2236,6 +2236,18 @@
   </si>
   <si>
     <t xml:space="preserve">5.Форма публикации закрыта, изменения не сохранены. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удалить новость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удадить новость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.Нажать на кнопку удаления новости</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.Новость удалена из публикаций</t>
   </si>
   <si>
     <t xml:space="preserve">Устройство</t>
@@ -3100,7 +3112,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3191,6 +3203,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3376,7 +3392,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J279"/>
+  <dimension ref="A1:J281"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.73"/>
@@ -7589,7 +7605,7 @@
         <v>366</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>13</v>
+        <v>197</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>230</v>
@@ -7668,81 +7684,71 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
     </row>
-    <row r="235" s="11" customFormat="true" ht="14.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="20" t="s">
+    <row r="235" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A235" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B235" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="B235" s="20"/>
-      <c r="C235" s="20"/>
-      <c r="D235" s="20"/>
-      <c r="E235" s="20"/>
-      <c r="F235" s="20"/>
-      <c r="G235" s="20"/>
-      <c r="H235" s="20"/>
-      <c r="I235" s="20"/>
-      <c r="J235" s="20"/>
-    </row>
-    <row r="236" s="11" customFormat="true" ht="160.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B236" s="17" t="s">
+      <c r="C235" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C236" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="D236" s="8" t="s">
+      <c r="D235" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E236" s="2" t="s">
+      <c r="E235" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H235" s="2"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="3"/>
+    </row>
+    <row r="236" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A236" s="1"/>
+      <c r="B236" s="23"/>
+      <c r="C236" s="23"/>
+      <c r="D236" s="8"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F236" s="2" t="s">
+      <c r="G236" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="G236" s="2" t="s">
+      <c r="H236" s="2"/>
+      <c r="I236" s="1"/>
+      <c r="J236" s="1"/>
+    </row>
+    <row r="237" s="11" customFormat="true" ht="14.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A237" s="20" t="s">
         <v>375</v>
       </c>
-      <c r="H236" s="2"/>
-      <c r="I236" s="3"/>
-      <c r="J236" s="3"/>
-    </row>
-    <row r="237" s="11" customFormat="true" ht="89.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="1" t="n">
+      <c r="B237" s="20"/>
+      <c r="C237" s="20"/>
+      <c r="D237" s="20"/>
+      <c r="E237" s="20"/>
+      <c r="F237" s="20"/>
+      <c r="G237" s="20"/>
+      <c r="H237" s="20"/>
+      <c r="I237" s="20"/>
+      <c r="J237" s="20"/>
+    </row>
+    <row r="238" s="11" customFormat="true" ht="160.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B237" s="17" t="s">
+      <c r="B238" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="C237" s="17" t="s">
+      <c r="C238" s="17" t="s">
         <v>376</v>
-      </c>
-      <c r="D237" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="G237" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H237" s="2"/>
-      <c r="I237" s="3"/>
-      <c r="J237" s="3"/>
-    </row>
-    <row r="238" s="11" customFormat="true" ht="43.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B238" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="C238" s="17" t="s">
-        <v>379</v>
       </c>
       <c r="D238" s="8" t="s">
         <v>13</v>
@@ -7751,79 +7757,99 @@
         <v>377</v>
       </c>
       <c r="F238" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H238" s="2"/>
+      <c r="I238" s="3"/>
+      <c r="J238" s="3"/>
+    </row>
+    <row r="239" s="11" customFormat="true" ht="89.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A239" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B239" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="G238" s="2" t="s">
+      <c r="C239" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="D239" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="H238" s="2"/>
-      <c r="I238" s="1"/>
-      <c r="J238" s="3"/>
-    </row>
-    <row r="239" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="1"/>
-      <c r="B239" s="17"/>
-      <c r="C239" s="17"/>
-      <c r="D239" s="8"/>
-      <c r="E239" s="2"/>
       <c r="F239" s="2" t="s">
         <v>382</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>383</v>
+        <v>27</v>
       </c>
       <c r="H239" s="2"/>
-      <c r="I239" s="1"/>
-      <c r="J239" s="1"/>
-    </row>
-    <row r="240" s="11" customFormat="true" ht="45.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I239" s="3"/>
+      <c r="J239" s="3"/>
+    </row>
+    <row r="240" s="11" customFormat="true" ht="43.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="n">
         <v>76</v>
       </c>
       <c r="B240" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C240" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D240" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E240" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G240" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F240" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="H240" s="2"/>
-      <c r="I240" s="3"/>
+      <c r="I240" s="1"/>
       <c r="J240" s="3"/>
     </row>
-    <row r="241" s="11" customFormat="true" ht="41.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="241" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1"/>
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
       <c r="D241" s="8"/>
       <c r="E241" s="2"/>
       <c r="F241" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H241" s="2"/>
+      <c r="I241" s="1"/>
+      <c r="J241" s="1"/>
+    </row>
+    <row r="242" s="11" customFormat="true" ht="45.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A242" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B242" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="G241" s="2" t="s">
+      <c r="C242" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="D242" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="H241" s="2"/>
-      <c r="I241" s="3"/>
-      <c r="J241" s="3"/>
-    </row>
-    <row r="242" s="11" customFormat="true" ht="41.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="1"/>
-      <c r="B242" s="17"/>
-      <c r="C242" s="17"/>
-      <c r="D242" s="8"/>
-      <c r="E242" s="2"/>
       <c r="F242" s="2" t="s">
         <v>390</v>
       </c>
@@ -7834,54 +7860,54 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
     </row>
-    <row r="243" s="11" customFormat="true" ht="44.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B243" s="17" t="s">
+    <row r="243" s="11" customFormat="true" ht="41.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A243" s="1"/>
+      <c r="B243" s="17"/>
+      <c r="C243" s="17"/>
+      <c r="D243" s="8"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C243" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="D243" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F243" s="2" t="s">
+      <c r="G243" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="G243" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="H243" s="2"/>
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
     </row>
-    <row r="244" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="244" s="11" customFormat="true" ht="41.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1"/>
       <c r="B244" s="17"/>
       <c r="C244" s="17"/>
       <c r="D244" s="8"/>
       <c r="E244" s="2"/>
       <c r="F244" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G244" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="G244" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="H244" s="2"/>
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
     </row>
-    <row r="245" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A245" s="1"/>
-      <c r="B245" s="17"/>
-      <c r="C245" s="17"/>
-      <c r="D245" s="8"/>
-      <c r="E245" s="2"/>
+    <row r="245" s="11" customFormat="true" ht="44.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A245" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B245" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="C245" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="D245" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>389</v>
+      </c>
       <c r="F245" s="2" t="s">
         <v>397</v>
       </c>
@@ -7892,7 +7918,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
     </row>
-    <row r="246" s="11" customFormat="true" ht="59.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="246" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1"/>
       <c r="B246" s="17"/>
       <c r="C246" s="17"/>
@@ -7908,69 +7934,69 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
     </row>
-    <row r="247" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B247" s="17" t="s">
+    <row r="247" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A247" s="1"/>
+      <c r="B247" s="17"/>
+      <c r="C247" s="17"/>
+      <c r="D247" s="8"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C247" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="D247" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F247" s="2" t="s">
+      <c r="G247" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="G247" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="H247" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="I247" s="16" t="s">
-        <v>405</v>
-      </c>
+      <c r="H247" s="2"/>
+      <c r="I247" s="3"/>
       <c r="J247" s="3"/>
     </row>
-    <row r="248" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="248" s="11" customFormat="true" ht="59.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1"/>
       <c r="B248" s="17"/>
       <c r="C248" s="17"/>
       <c r="D248" s="8"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="H248" s="2"/>
+      <c r="I248" s="3"/>
+      <c r="J248" s="3"/>
+    </row>
+    <row r="249" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A249" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B249" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="C249" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="G248" s="2" t="s">
+      <c r="G249" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="H248" s="2"/>
-      <c r="I248" s="16"/>
-      <c r="J248" s="16"/>
-    </row>
-    <row r="249" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A249" s="1"/>
-      <c r="B249" s="17"/>
-      <c r="C249" s="17"/>
-      <c r="D249" s="8"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2" t="s">
+      <c r="H249" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G249" s="2" t="s">
+      <c r="I249" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="H249" s="2"/>
-      <c r="I249" s="16"/>
-      <c r="J249" s="16"/>
-    </row>
-    <row r="250" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J249" s="3"/>
+    </row>
+    <row r="250" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1"/>
       <c r="B250" s="17"/>
       <c r="C250" s="17"/>
@@ -7986,33 +8012,23 @@
       <c r="I250" s="16"/>
       <c r="J250" s="16"/>
     </row>
-    <row r="251" s="11" customFormat="true" ht="52.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A251" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B251" s="17" t="s">
+    <row r="251" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A251" s="1"/>
+      <c r="B251" s="17"/>
+      <c r="C251" s="17"/>
+      <c r="D251" s="8"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C251" s="17" t="s">
-        <v>412</v>
-      </c>
-      <c r="D251" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F251" s="2" t="s">
+      <c r="G251" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="G251" s="2" t="s">
-        <v>403</v>
-      </c>
       <c r="H251" s="2"/>
-      <c r="I251" s="3"/>
-      <c r="J251" s="3"/>
-    </row>
-    <row r="252" s="11" customFormat="true" ht="64.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I251" s="16"/>
+      <c r="J251" s="16"/>
+    </row>
+    <row r="252" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1"/>
       <c r="B252" s="17"/>
       <c r="C252" s="17"/>
@@ -8025,10 +8041,10 @@
         <v>415</v>
       </c>
       <c r="H252" s="2"/>
-      <c r="I252" s="3"/>
-      <c r="J252" s="3"/>
-    </row>
-    <row r="253" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I252" s="16"/>
+      <c r="J252" s="16"/>
+    </row>
+    <row r="253" s="11" customFormat="true" ht="52.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="n">
         <v>80</v>
       </c>
@@ -8042,29 +8058,29 @@
         <v>13</v>
       </c>
       <c r="E253" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F253" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="F253" s="2" t="s">
-        <v>418</v>
-      </c>
       <c r="G253" s="2" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="H253" s="2"/>
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
     </row>
-    <row r="254" s="11" customFormat="true" ht="107.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="254" s="11" customFormat="true" ht="64.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1"/>
       <c r="B254" s="17"/>
       <c r="C254" s="17"/>
       <c r="D254" s="8"/>
       <c r="E254" s="2"/>
       <c r="F254" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H254" s="2"/>
       <c r="I254" s="3"/>
@@ -8075,38 +8091,38 @@
         <v>81</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C255" s="17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D255" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F255" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G255" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="G255" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="H255" s="2"/>
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
     </row>
-    <row r="256" s="11" customFormat="true" ht="110.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="256" s="11" customFormat="true" ht="107.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1"/>
       <c r="B256" s="17"/>
       <c r="C256" s="17"/>
       <c r="D256" s="8"/>
       <c r="E256" s="2"/>
       <c r="F256" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G256" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="G256" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="H256" s="2"/>
       <c r="I256" s="3"/>
@@ -8117,49 +8133,59 @@
         <v>82</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C257" s="17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D257" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E257" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G257" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="G257" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="H257" s="2"/>
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
     </row>
-    <row r="258" s="11" customFormat="true" ht="43.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="258" s="11" customFormat="true" ht="110.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1"/>
       <c r="B258" s="17"/>
       <c r="C258" s="17"/>
       <c r="D258" s="8"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H258" s="2"/>
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
     </row>
-    <row r="259" s="11" customFormat="true" ht="83.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="1"/>
-      <c r="B259" s="17"/>
-      <c r="C259" s="17"/>
-      <c r="D259" s="8"/>
-      <c r="E259" s="2"/>
+    <row r="259" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A259" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B259" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="C259" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>432</v>
+      </c>
       <c r="F259" s="2" t="s">
         <v>433</v>
       </c>
@@ -8170,54 +8196,54 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
     </row>
-    <row r="260" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B260" s="17" t="s">
+    <row r="260" s="11" customFormat="true" ht="43.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A260" s="1"/>
+      <c r="B260" s="17"/>
+      <c r="C260" s="17"/>
+      <c r="D260" s="8"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C260" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="D260" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E260" s="2" t="s">
+      <c r="G260" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="H260" s="2"/>
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
     </row>
-    <row r="261" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="261" s="11" customFormat="true" ht="83.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1"/>
       <c r="B261" s="17"/>
       <c r="C261" s="17"/>
       <c r="D261" s="8"/>
       <c r="E261" s="2"/>
       <c r="F261" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H261" s="2"/>
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
     </row>
-    <row r="262" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="1"/>
-      <c r="B262" s="17"/>
-      <c r="C262" s="17"/>
-      <c r="D262" s="8"/>
-      <c r="E262" s="2"/>
+    <row r="262" s="11" customFormat="true" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A262" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B262" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="C262" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>440</v>
+      </c>
       <c r="F262" s="2" t="s">
         <v>441</v>
       </c>
@@ -8228,7 +8254,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
     </row>
-    <row r="263" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="263" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1"/>
       <c r="B263" s="17"/>
       <c r="C263" s="17"/>
@@ -8244,7 +8270,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
     </row>
-    <row r="264" s="11" customFormat="true" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="264" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1"/>
       <c r="B264" s="17"/>
       <c r="C264" s="17"/>
@@ -8260,54 +8286,54 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
     </row>
-    <row r="265" s="11" customFormat="true" ht="71.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A265" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B265" s="17" t="s">
+    <row r="265" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A265" s="1"/>
+      <c r="B265" s="17"/>
+      <c r="C265" s="17"/>
+      <c r="D265" s="8"/>
+      <c r="E265" s="2"/>
+      <c r="F265" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C265" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="D265" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E265" s="2" t="s">
+      <c r="G265" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G265" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="H265" s="2"/>
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
     </row>
-    <row r="266" s="11" customFormat="true" ht="71.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="266" s="11" customFormat="true" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1"/>
       <c r="B266" s="17"/>
       <c r="C266" s="17"/>
       <c r="D266" s="8"/>
       <c r="E266" s="2"/>
       <c r="F266" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H266" s="2"/>
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
     </row>
-    <row r="267" s="11" customFormat="true" ht="62.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="1"/>
-      <c r="B267" s="17"/>
-      <c r="C267" s="17"/>
-      <c r="D267" s="8"/>
-      <c r="E267" s="2"/>
+    <row r="267" s="11" customFormat="true" ht="71.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A267" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B267" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="C267" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>452</v>
+      </c>
       <c r="F267" s="2" t="s">
         <v>453</v>
       </c>
@@ -8318,54 +8344,54 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
     </row>
-    <row r="268" s="11" customFormat="true" ht="75.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B268" s="17" t="s">
+    <row r="268" s="11" customFormat="true" ht="71.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A268" s="1"/>
+      <c r="B268" s="17"/>
+      <c r="C268" s="17"/>
+      <c r="D268" s="8"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C268" s="17" t="s">
-        <v>455</v>
-      </c>
-      <c r="D268" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E268" s="2" t="s">
+      <c r="G268" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G268" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="H268" s="2"/>
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
     </row>
-    <row r="269" s="11" customFormat="true" ht="51.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="269" s="11" customFormat="true" ht="62.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1"/>
       <c r="B269" s="17"/>
       <c r="C269" s="17"/>
       <c r="D269" s="8"/>
       <c r="E269" s="2"/>
       <c r="F269" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="H269" s="2"/>
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
     </row>
-    <row r="270" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A270" s="1"/>
-      <c r="B270" s="17"/>
-      <c r="C270" s="17"/>
-      <c r="D270" s="8"/>
-      <c r="E270" s="2"/>
+    <row r="270" s="11" customFormat="true" ht="75.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A270" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B270" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="C270" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>460</v>
+      </c>
       <c r="F270" s="2" t="s">
         <v>453</v>
       </c>
@@ -8376,54 +8402,54 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
     </row>
-    <row r="271" s="11" customFormat="true" ht="70.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B271" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="C271" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="D271" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>458</v>
-      </c>
+    <row r="271" s="11" customFormat="true" ht="51.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A271" s="1"/>
+      <c r="B271" s="17"/>
+      <c r="C271" s="17"/>
+      <c r="D271" s="8"/>
+      <c r="E271" s="2"/>
       <c r="F271" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="H271" s="2"/>
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
     </row>
-    <row r="272" s="11" customFormat="true" ht="46.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="272" s="11" customFormat="true" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1"/>
       <c r="B272" s="17"/>
       <c r="C272" s="17"/>
       <c r="D272" s="8"/>
       <c r="E272" s="2"/>
       <c r="F272" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="H272" s="2"/>
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
     </row>
-    <row r="273" s="11" customFormat="true" ht="46.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A273" s="1"/>
-      <c r="B273" s="17"/>
-      <c r="C273" s="17"/>
-      <c r="D273" s="8"/>
-      <c r="E273" s="2"/>
+    <row r="273" s="11" customFormat="true" ht="70.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A273" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B273" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="C273" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>462</v>
+      </c>
       <c r="F273" s="2" t="s">
         <v>453</v>
       </c>
@@ -8434,126 +8460,158 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
     </row>
-    <row r="274" s="11" customFormat="true" ht="69.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A274" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B274" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="C274" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="D274" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>460</v>
-      </c>
+    <row r="274" s="11" customFormat="true" ht="46.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A274" s="1"/>
+      <c r="B274" s="17"/>
+      <c r="C274" s="17"/>
+      <c r="D274" s="8"/>
+      <c r="E274" s="2"/>
       <c r="F274" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="H274" s="2" t="s">
-        <v>462</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="H274" s="2"/>
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
     </row>
-    <row r="275" s="11" customFormat="true" ht="53.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="275" s="11" customFormat="true" ht="46.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1"/>
       <c r="B275" s="17"/>
       <c r="C275" s="17"/>
       <c r="D275" s="8"/>
       <c r="E275" s="2"/>
       <c r="F275" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="H275" s="2"/>
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
     </row>
-    <row r="276" s="11" customFormat="true" ht="56.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A276" s="1"/>
-      <c r="B276" s="17"/>
-      <c r="C276" s="17"/>
-      <c r="D276" s="8"/>
-      <c r="E276" s="2"/>
+    <row r="276" s="11" customFormat="true" ht="69.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A276" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B276" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="C276" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>464</v>
+      </c>
       <c r="F276" s="2" t="s">
         <v>453</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="H276" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="H276" s="2" t="s">
+        <v>466</v>
+      </c>
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
     </row>
-    <row r="277" s="11" customFormat="true" ht="51.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A277" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B277" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="C277" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="D277" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>466</v>
-      </c>
+    <row r="277" s="11" customFormat="true" ht="53.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A277" s="1"/>
+      <c r="B277" s="17"/>
+      <c r="C277" s="17"/>
+      <c r="D277" s="8"/>
+      <c r="E277" s="2"/>
       <c r="F277" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="H277" s="2"/>
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
     </row>
-    <row r="278" s="11" customFormat="true" ht="67.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="278" s="11" customFormat="true" ht="56.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1"/>
       <c r="B278" s="17"/>
       <c r="C278" s="17"/>
       <c r="D278" s="8"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H278" s="2"/>
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
     </row>
-    <row r="279" s="11" customFormat="true" ht="63.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A279" s="1"/>
-      <c r="B279" s="17"/>
-      <c r="C279" s="17"/>
-      <c r="D279" s="8"/>
-      <c r="E279" s="2"/>
+    <row r="279" s="11" customFormat="true" ht="51.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A279" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B279" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="C279" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>470</v>
+      </c>
       <c r="F279" s="2" t="s">
         <v>453</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H279" s="2"/>
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
     </row>
+    <row r="280" s="11" customFormat="true" ht="67.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A280" s="1"/>
+      <c r="B280" s="17"/>
+      <c r="C280" s="17"/>
+      <c r="D280" s="8"/>
+      <c r="E280" s="2"/>
+      <c r="F280" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H280" s="2"/>
+      <c r="I280" s="3"/>
+      <c r="J280" s="3"/>
+    </row>
+    <row r="281" s="11" customFormat="true" ht="63.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A281" s="1"/>
+      <c r="B281" s="17"/>
+      <c r="C281" s="17"/>
+      <c r="D281" s="8"/>
+      <c r="E281" s="2"/>
+      <c r="F281" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H281" s="2"/>
+      <c r="I281" s="3"/>
+      <c r="J281" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="628">
+  <mergeCells count="636">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B3:B6"/>
@@ -9069,47 +9127,47 @@
     <mergeCell ref="H230:H234"/>
     <mergeCell ref="I230:I234"/>
     <mergeCell ref="J230:J234"/>
-    <mergeCell ref="A235:J235"/>
-    <mergeCell ref="A238:A239"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="C238:C239"/>
-    <mergeCell ref="D238:D239"/>
-    <mergeCell ref="E238:E239"/>
-    <mergeCell ref="H238:H239"/>
-    <mergeCell ref="I238:I239"/>
-    <mergeCell ref="J238:J239"/>
-    <mergeCell ref="A240:A242"/>
-    <mergeCell ref="B240:B242"/>
-    <mergeCell ref="C240:C242"/>
-    <mergeCell ref="D240:D242"/>
-    <mergeCell ref="E240:E242"/>
-    <mergeCell ref="H240:H242"/>
-    <mergeCell ref="I240:I242"/>
-    <mergeCell ref="J240:J242"/>
-    <mergeCell ref="A243:A246"/>
-    <mergeCell ref="B243:B246"/>
-    <mergeCell ref="C243:C246"/>
-    <mergeCell ref="D243:D246"/>
-    <mergeCell ref="E243:E246"/>
-    <mergeCell ref="H243:H246"/>
-    <mergeCell ref="I243:I246"/>
-    <mergeCell ref="J243:J246"/>
-    <mergeCell ref="A247:A250"/>
-    <mergeCell ref="B247:B250"/>
-    <mergeCell ref="C247:C250"/>
-    <mergeCell ref="D247:D250"/>
-    <mergeCell ref="E247:E250"/>
-    <mergeCell ref="H247:H250"/>
-    <mergeCell ref="I247:I250"/>
-    <mergeCell ref="J247:J250"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="C251:C252"/>
-    <mergeCell ref="D251:D252"/>
-    <mergeCell ref="E251:E252"/>
-    <mergeCell ref="H251:H252"/>
-    <mergeCell ref="I251:I252"/>
-    <mergeCell ref="J251:J252"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="B235:B236"/>
+    <mergeCell ref="C235:C236"/>
+    <mergeCell ref="D235:D236"/>
+    <mergeCell ref="E235:E236"/>
+    <mergeCell ref="H235:H236"/>
+    <mergeCell ref="I235:I236"/>
+    <mergeCell ref="J235:J236"/>
+    <mergeCell ref="A237:J237"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="E240:E241"/>
+    <mergeCell ref="H240:H241"/>
+    <mergeCell ref="I240:I241"/>
+    <mergeCell ref="J240:J241"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="B242:B244"/>
+    <mergeCell ref="C242:C244"/>
+    <mergeCell ref="D242:D244"/>
+    <mergeCell ref="E242:E244"/>
+    <mergeCell ref="H242:H244"/>
+    <mergeCell ref="I242:I244"/>
+    <mergeCell ref="J242:J244"/>
+    <mergeCell ref="A245:A248"/>
+    <mergeCell ref="B245:B248"/>
+    <mergeCell ref="C245:C248"/>
+    <mergeCell ref="D245:D248"/>
+    <mergeCell ref="E245:E248"/>
+    <mergeCell ref="H245:H248"/>
+    <mergeCell ref="I245:I248"/>
+    <mergeCell ref="J245:J248"/>
+    <mergeCell ref="A249:A252"/>
+    <mergeCell ref="B249:B252"/>
+    <mergeCell ref="C249:C252"/>
+    <mergeCell ref="D249:D252"/>
+    <mergeCell ref="E249:E252"/>
+    <mergeCell ref="H249:H252"/>
+    <mergeCell ref="I249:I252"/>
+    <mergeCell ref="J249:J252"/>
     <mergeCell ref="A253:A254"/>
     <mergeCell ref="B253:B254"/>
     <mergeCell ref="C253:C254"/>
@@ -9126,65 +9184,73 @@
     <mergeCell ref="H255:H256"/>
     <mergeCell ref="I255:I256"/>
     <mergeCell ref="J255:J256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="B257:B259"/>
-    <mergeCell ref="C257:C259"/>
-    <mergeCell ref="D257:D259"/>
-    <mergeCell ref="E257:E259"/>
-    <mergeCell ref="H257:H259"/>
-    <mergeCell ref="I257:I259"/>
-    <mergeCell ref="J257:J259"/>
-    <mergeCell ref="A260:A264"/>
-    <mergeCell ref="B260:B264"/>
-    <mergeCell ref="C260:C264"/>
-    <mergeCell ref="D260:D264"/>
-    <mergeCell ref="E260:E264"/>
-    <mergeCell ref="H260:H264"/>
-    <mergeCell ref="I260:I264"/>
-    <mergeCell ref="J260:J264"/>
-    <mergeCell ref="A265:A267"/>
-    <mergeCell ref="B265:B267"/>
-    <mergeCell ref="C265:C267"/>
-    <mergeCell ref="D265:D267"/>
-    <mergeCell ref="E265:E267"/>
-    <mergeCell ref="H265:H267"/>
-    <mergeCell ref="I265:I267"/>
-    <mergeCell ref="J265:J267"/>
-    <mergeCell ref="A268:A270"/>
-    <mergeCell ref="B268:B270"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="D268:D270"/>
-    <mergeCell ref="E268:E270"/>
-    <mergeCell ref="H268:H270"/>
-    <mergeCell ref="I268:I270"/>
-    <mergeCell ref="J268:J270"/>
-    <mergeCell ref="A271:A273"/>
-    <mergeCell ref="B271:B273"/>
-    <mergeCell ref="C271:C273"/>
-    <mergeCell ref="D271:D273"/>
-    <mergeCell ref="E271:E273"/>
-    <mergeCell ref="H271:H273"/>
-    <mergeCell ref="I271:I273"/>
-    <mergeCell ref="J271:J273"/>
-    <mergeCell ref="A274:A276"/>
-    <mergeCell ref="B274:B276"/>
-    <mergeCell ref="C274:C276"/>
-    <mergeCell ref="D274:D276"/>
-    <mergeCell ref="E274:E276"/>
-    <mergeCell ref="H274:H276"/>
-    <mergeCell ref="I274:I276"/>
-    <mergeCell ref="J274:J276"/>
-    <mergeCell ref="A277:A279"/>
-    <mergeCell ref="B277:B279"/>
-    <mergeCell ref="C277:C279"/>
-    <mergeCell ref="D277:D279"/>
-    <mergeCell ref="E277:E279"/>
-    <mergeCell ref="H277:H279"/>
-    <mergeCell ref="I277:I279"/>
-    <mergeCell ref="J277:J279"/>
+    <mergeCell ref="A257:A258"/>
+    <mergeCell ref="B257:B258"/>
+    <mergeCell ref="C257:C258"/>
+    <mergeCell ref="D257:D258"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="H257:H258"/>
+    <mergeCell ref="I257:I258"/>
+    <mergeCell ref="J257:J258"/>
+    <mergeCell ref="A259:A261"/>
+    <mergeCell ref="B259:B261"/>
+    <mergeCell ref="C259:C261"/>
+    <mergeCell ref="D259:D261"/>
+    <mergeCell ref="E259:E261"/>
+    <mergeCell ref="H259:H261"/>
+    <mergeCell ref="I259:I261"/>
+    <mergeCell ref="J259:J261"/>
+    <mergeCell ref="A262:A266"/>
+    <mergeCell ref="B262:B266"/>
+    <mergeCell ref="C262:C266"/>
+    <mergeCell ref="D262:D266"/>
+    <mergeCell ref="E262:E266"/>
+    <mergeCell ref="H262:H266"/>
+    <mergeCell ref="I262:I266"/>
+    <mergeCell ref="J262:J266"/>
+    <mergeCell ref="A267:A269"/>
+    <mergeCell ref="B267:B269"/>
+    <mergeCell ref="C267:C269"/>
+    <mergeCell ref="D267:D269"/>
+    <mergeCell ref="E267:E269"/>
+    <mergeCell ref="H267:H269"/>
+    <mergeCell ref="I267:I269"/>
+    <mergeCell ref="J267:J269"/>
+    <mergeCell ref="A270:A272"/>
+    <mergeCell ref="B270:B272"/>
+    <mergeCell ref="C270:C272"/>
+    <mergeCell ref="D270:D272"/>
+    <mergeCell ref="E270:E272"/>
+    <mergeCell ref="H270:H272"/>
+    <mergeCell ref="I270:I272"/>
+    <mergeCell ref="J270:J272"/>
+    <mergeCell ref="A273:A275"/>
+    <mergeCell ref="B273:B275"/>
+    <mergeCell ref="C273:C275"/>
+    <mergeCell ref="D273:D275"/>
+    <mergeCell ref="E273:E275"/>
+    <mergeCell ref="H273:H275"/>
+    <mergeCell ref="I273:I275"/>
+    <mergeCell ref="J273:J275"/>
+    <mergeCell ref="A276:A278"/>
+    <mergeCell ref="B276:B278"/>
+    <mergeCell ref="C276:C278"/>
+    <mergeCell ref="D276:D278"/>
+    <mergeCell ref="E276:E278"/>
+    <mergeCell ref="H276:H278"/>
+    <mergeCell ref="I276:I278"/>
+    <mergeCell ref="J276:J278"/>
+    <mergeCell ref="A279:A281"/>
+    <mergeCell ref="B279:B281"/>
+    <mergeCell ref="C279:C281"/>
+    <mergeCell ref="D279:D281"/>
+    <mergeCell ref="E279:E281"/>
+    <mergeCell ref="H279:H281"/>
+    <mergeCell ref="I279:I281"/>
+    <mergeCell ref="J279:J281"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D3 D7:D10 D12 D15 D18 D21 D24 D27 D30 D33 D37:D44 D46 D48 D51:D57 D59 D61 D64:D66 D68:D75 D77 D79 D81 D86 D89 D93 D97 D102 D106:D107 D109 D111 D117 D119 D122 D125 D131 D137 D143 D150 D156:D157 D162 D168 D173 D178 D183 D188:D191 D195 D199 D203 D207 D211 D214 D218 D222 D226 D230 D236:D240 D243 D247 D251 D253 D255 D257 D260 D265:D266 D268 D271 D274 D277" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D3 D7:D10 D12 D15 D18 D21 D24 D27 D30 D33 D37:D44 D46 D48 D51:D57 D59 D61 D64:D66 D68:D75 D77 D79 D81 D86 D89 D93 D97 D102 D106:D107 D109 D111 D117 D119 D122 D125 D131 D137 D143 D150 D156:D157 D162 D168 D173 D178 D183 D188:D191 D195 D199 D203 D207 D211 D214 D218 D222 D226 D230 D238:D242 D245 D249 D253 D255 D257 D259 D262 D267:D268 D270 D273 D276 D279" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9193,7 +9259,7 @@
     <hyperlink ref="I64" r:id="rId1" display="https://i.postimg.cc/GtYKj0Dg/Snimok-ekrana-2026-02-17-211615.png"/>
     <hyperlink ref="I65" r:id="rId2" display="https://i.postimg.cc/BZDBk08D/Snimok-ekrana-2026-02-17-212140.png"/>
     <hyperlink ref="I150" r:id="rId3" display="https://i.postimg.cc/KzQvx3GG/Snimok-ekrana-2026-02-20-172936.png"/>
-    <hyperlink ref="I247" r:id="rId4" display="https://radikal.cloud/i/%D0%A1%D0%BD%D0%B8%D0%BC%D0%BE%D0%BA-%D1%8D%D0%BA%D1%80%D0%B0%D0%BD%D0%B0-2026-02-22-131448.Era7KO"/>
+    <hyperlink ref="I249" r:id="rId4" display="https://radikal.cloud/i/%D0%A1%D0%BD%D0%B8%D0%BC%D0%BE%D0%BA-%D1%8D%D0%BA%D1%80%D0%B0%D0%BD%D0%B0-2026-02-22-131448.Era7KO"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -9731,7 +9797,7 @@
         <v>84</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9812,7 +9878,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -9829,10 +9895,10 @@
         <v>13</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>13</v>
@@ -9847,10 +9913,10 @@
         <v>95</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9871,10 +9937,10 @@
       <c r="C39" s="17"/>
       <c r="D39" s="8"/>
       <c r="F39" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="I39" s="16"/>
       <c r="J39" s="16"/>
@@ -9884,10 +9950,10 @@
       <c r="C40" s="17"/>
       <c r="D40" s="8"/>
       <c r="F40" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="16"/>
@@ -9897,10 +9963,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>13</v>
@@ -9935,10 +10001,10 @@
       <c r="C43" s="17"/>
       <c r="D43" s="8"/>
       <c r="F43" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
@@ -9948,10 +10014,10 @@
       <c r="C44" s="17"/>
       <c r="D44" s="8"/>
       <c r="F44" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="I44" s="16"/>
       <c r="J44" s="16"/>
@@ -9961,10 +10027,10 @@
       <c r="C45" s="17"/>
       <c r="D45" s="8"/>
       <c r="F45" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="I45" s="16"/>
       <c r="J45" s="16"/>
@@ -9974,10 +10040,10 @@
       <c r="C46" s="17"/>
       <c r="D46" s="8"/>
       <c r="F46" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="16"/>
@@ -10056,7 +10122,7 @@
         <v>17</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>116</v>
@@ -10139,7 +10205,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>13</v>
@@ -11405,7 +11471,7 @@
       <c r="C138" s="17"/>
       <c r="D138" s="8"/>
       <c r="F138" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>273</v>
@@ -11418,7 +11484,7 @@
       <c r="C139" s="17"/>
       <c r="D139" s="8"/>
       <c r="F139" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>275</v>
@@ -11457,10 +11523,10 @@
         <v>43</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D142" s="8" t="s">
         <v>13</v>
@@ -11481,10 +11547,10 @@
         <v>44</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D143" s="8" t="s">
         <v>197</v>
@@ -11505,7 +11571,7 @@
       <c r="C144" s="17"/>
       <c r="D144" s="8"/>
       <c r="F144" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>288</v>
@@ -11517,10 +11583,10 @@
       <c r="C145" s="17"/>
       <c r="D145" s="8"/>
       <c r="F145" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K145" s="11"/>
     </row>
@@ -11553,10 +11619,10 @@
         <v>45</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>197</v>
@@ -11589,7 +11655,7 @@
       <c r="C150" s="17"/>
       <c r="D150" s="8"/>
       <c r="F150" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>273</v>
@@ -11601,7 +11667,7 @@
       <c r="C151" s="17"/>
       <c r="D151" s="8"/>
       <c r="F151" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>275</v>
@@ -11637,10 +11703,10 @@
         <v>46</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>197</v>
@@ -11661,7 +11727,7 @@
       <c r="C155" s="17"/>
       <c r="D155" s="8"/>
       <c r="F155" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>288</v>
@@ -11673,7 +11739,7 @@
       <c r="C156" s="17"/>
       <c r="D156" s="8"/>
       <c r="F156" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>290</v>
@@ -11709,10 +11775,10 @@
         <v>47</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>197</v>
@@ -11741,7 +11807,7 @@
     <row r="161" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D161" s="8"/>
       <c r="F161" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>290</v>
@@ -11773,10 +11839,10 @@
         <v>48</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>197</v>
@@ -11805,7 +11871,7 @@
     <row r="166" customFormat="false" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D166" s="8"/>
       <c r="F166" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>273</v>
@@ -11869,7 +11935,7 @@
     <row r="171" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D171" s="8"/>
       <c r="F171" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>273</v>
@@ -11879,7 +11945,7 @@
     <row r="172" customFormat="false" ht="39.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D172" s="8"/>
       <c r="F172" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>275</v>
@@ -12578,7 +12644,7 @@
     </row>
     <row r="221" customFormat="false" ht="14.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="20" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -12596,22 +12662,22 @@
         <v>62</v>
       </c>
       <c r="B222" s="17" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C222" s="17" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K222" s="11"/>
     </row>
@@ -12620,19 +12686,19 @@
         <v>63</v>
       </c>
       <c r="B223" s="17" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C223" s="17" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D223" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>27</v>
@@ -12644,22 +12710,22 @@
         <v>64</v>
       </c>
       <c r="B224" s="17" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C224" s="17" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D224" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I224" s="1"/>
       <c r="K224" s="11"/>
@@ -12669,10 +12735,10 @@
       <c r="C225" s="17"/>
       <c r="D225" s="8"/>
       <c r="F225" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
@@ -12683,22 +12749,22 @@
         <v>65</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C226" s="17" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K226" s="11"/>
     </row>
@@ -12707,10 +12773,10 @@
       <c r="C227" s="17"/>
       <c r="D227" s="8"/>
       <c r="F227" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K227" s="11"/>
     </row>
@@ -12719,10 +12785,10 @@
       <c r="C228" s="17"/>
       <c r="D228" s="8"/>
       <c r="F228" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K228" s="11"/>
     </row>
@@ -12731,22 +12797,22 @@
         <v>66</v>
       </c>
       <c r="B229" s="17" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C229" s="17" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D229" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="K229" s="11"/>
     </row>
@@ -12755,10 +12821,10 @@
       <c r="C230" s="17"/>
       <c r="D230" s="8"/>
       <c r="F230" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="K230" s="11"/>
     </row>
@@ -12767,10 +12833,10 @@
       <c r="C231" s="17"/>
       <c r="D231" s="8"/>
       <c r="F231" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="K231" s="11"/>
     </row>
@@ -12779,10 +12845,10 @@
       <c r="C232" s="17"/>
       <c r="D232" s="8"/>
       <c r="F232" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="K232" s="11"/>
     </row>
@@ -12791,28 +12857,28 @@
         <v>67</v>
       </c>
       <c r="B233" s="17" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C233" s="17" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D233" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="I233" s="16" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K233" s="11"/>
     </row>
@@ -12821,10 +12887,10 @@
       <c r="C234" s="17"/>
       <c r="D234" s="8"/>
       <c r="F234" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I234" s="16"/>
       <c r="J234" s="16"/>
@@ -12835,10 +12901,10 @@
       <c r="C235" s="17"/>
       <c r="D235" s="8"/>
       <c r="F235" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I235" s="16"/>
       <c r="J235" s="16"/>
@@ -12849,10 +12915,10 @@
       <c r="C236" s="17"/>
       <c r="D236" s="8"/>
       <c r="F236" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I236" s="16"/>
       <c r="J236" s="16"/>
@@ -12863,22 +12929,22 @@
         <v>68</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C237" s="17" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D237" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K237" s="11"/>
     </row>
@@ -12887,10 +12953,10 @@
       <c r="C238" s="17"/>
       <c r="D238" s="8"/>
       <c r="F238" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="K238" s="11"/>
     </row>
@@ -12899,22 +12965,22 @@
         <v>69</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C239" s="17" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D239" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K239" s="11"/>
     </row>
@@ -12923,10 +12989,10 @@
       <c r="C240" s="17"/>
       <c r="D240" s="8"/>
       <c r="F240" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K240" s="11"/>
     </row>
@@ -12935,22 +13001,22 @@
         <v>70</v>
       </c>
       <c r="B241" s="17" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C241" s="17" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D241" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="K241" s="11"/>
     </row>
@@ -12959,10 +13025,10 @@
       <c r="C242" s="17"/>
       <c r="D242" s="8"/>
       <c r="F242" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="K242" s="11"/>
     </row>
@@ -12971,22 +13037,22 @@
         <v>71</v>
       </c>
       <c r="B243" s="17" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C243" s="17" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D243" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="K243" s="11"/>
     </row>
@@ -12995,10 +13061,10 @@
       <c r="C244" s="17"/>
       <c r="D244" s="8"/>
       <c r="F244" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="K244" s="11"/>
     </row>
@@ -13007,10 +13073,10 @@
       <c r="C245" s="17"/>
       <c r="D245" s="8"/>
       <c r="F245" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="K245" s="11"/>
     </row>
@@ -13019,22 +13085,22 @@
         <v>72</v>
       </c>
       <c r="B246" s="17" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C246" s="17" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D246" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="K246" s="11"/>
     </row>
@@ -13043,10 +13109,10 @@
       <c r="C247" s="17"/>
       <c r="D247" s="8"/>
       <c r="F247" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="K247" s="11"/>
     </row>
@@ -13055,10 +13121,10 @@
       <c r="C248" s="17"/>
       <c r="D248" s="8"/>
       <c r="F248" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="K248" s="11"/>
     </row>
@@ -13067,10 +13133,10 @@
       <c r="C249" s="17"/>
       <c r="D249" s="8"/>
       <c r="F249" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K249" s="11"/>
     </row>
@@ -13079,10 +13145,10 @@
       <c r="C250" s="17"/>
       <c r="D250" s="8"/>
       <c r="F250" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="K250" s="11"/>
     </row>
@@ -13091,22 +13157,22 @@
         <v>73</v>
       </c>
       <c r="B251" s="17" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C251" s="17" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K251" s="11"/>
     </row>
@@ -13115,10 +13181,10 @@
       <c r="C252" s="17"/>
       <c r="D252" s="8"/>
       <c r="F252" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="K252" s="11"/>
     </row>
@@ -13127,10 +13193,10 @@
       <c r="C253" s="17"/>
       <c r="D253" s="8"/>
       <c r="F253" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="K253" s="11"/>
     </row>
@@ -13139,22 +13205,22 @@
         <v>74</v>
       </c>
       <c r="B254" s="17" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C254" s="17" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D254" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K254" s="11"/>
     </row>
@@ -13163,10 +13229,10 @@
       <c r="C255" s="17"/>
       <c r="D255" s="8"/>
       <c r="F255" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="K255" s="11"/>
     </row>
@@ -13175,10 +13241,10 @@
       <c r="C256" s="17"/>
       <c r="D256" s="8"/>
       <c r="F256" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="K256" s="11"/>
     </row>
@@ -13187,22 +13253,22 @@
         <v>75</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C257" s="17" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D257" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K257" s="11"/>
     </row>
@@ -13211,10 +13277,10 @@
       <c r="C258" s="17"/>
       <c r="D258" s="8"/>
       <c r="F258" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="K258" s="11"/>
     </row>
@@ -13223,10 +13289,10 @@
       <c r="C259" s="17"/>
       <c r="D259" s="8"/>
       <c r="F259" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="K259" s="11"/>
     </row>
@@ -13235,25 +13301,25 @@
         <v>76</v>
       </c>
       <c r="B260" s="17" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C260" s="17" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K260" s="11"/>
     </row>
@@ -13262,10 +13328,10 @@
       <c r="C261" s="17"/>
       <c r="D261" s="8"/>
       <c r="F261" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="K261" s="11"/>
     </row>
@@ -13274,10 +13340,10 @@
       <c r="C262" s="17"/>
       <c r="D262" s="8"/>
       <c r="F262" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="K262" s="11"/>
     </row>
@@ -13286,22 +13352,22 @@
         <v>77</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C263" s="17" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D263" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="K263" s="11"/>
     </row>
@@ -13310,10 +13376,10 @@
       <c r="C264" s="17"/>
       <c r="D264" s="8"/>
       <c r="F264" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K264" s="11"/>
     </row>
@@ -13322,10 +13388,10 @@
       <c r="C265" s="17"/>
       <c r="D265" s="8"/>
       <c r="F265" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="K265" s="11"/>
     </row>

--- a/documentation/Cases.xlsx
+++ b/documentation/Cases.xlsx
@@ -795,7 +795,7 @@
     <t xml:space="preserve">1.Кнопка не кликабельна, пользователь остается на этой же странице.</t>
   </si>
   <si>
-    <t xml:space="preserve">Кнопка кликабельна</t>
+    <t xml:space="preserve">Кнопка кликабельна, но пользователь остается на странице.</t>
   </si>
   <si>
     <r>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">News</t>
   </si>
   <si>
-    <t xml:space="preserve">Отсутствие перехода на страницу News через кнопку Menu</t>
+    <t xml:space="preserve">Отсутствие кликабельности кнопки News в Menu на странице новостей</t>
   </si>
   <si>
     <t xml:space="preserve">1.Пройти авторизацию в приложении «Мобильный хоспис».
@@ -1267,6 +1267,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.Открыта страница «Control panel»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Просмотр новостей на странице Control panel</t>
   </si>
   <si>
     <r>
@@ -2239,9 +2242,6 @@
   </si>
   <si>
     <t xml:space="preserve">Удалить новость</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Удадить новость</t>
   </si>
   <si>
     <t xml:space="preserve">2.Нажать на кнопку удаления новости</t>
@@ -3057,7 +3057,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3067,6 +3067,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE8CB"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3CAC7"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
@@ -3112,7 +3124,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3165,7 +3177,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3197,7 +3209,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3205,8 +3221,12 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3234,7 +3254,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFB3CAC7"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -4771,7 +4791,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="37.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="13" t="n">
         <v>34</v>
       </c>
       <c r="B77" s="17" t="s">
@@ -4794,6 +4814,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="39.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="13"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
       <c r="D78" s="8"/>
@@ -4805,7 +4826,7 @@
       </c>
     </row>
     <row r="79" s="11" customFormat="true" ht="37.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="21" t="n">
         <v>35</v>
       </c>
       <c r="B79" s="17" t="s">
@@ -4831,7 +4852,7 @@
       <c r="J79" s="3"/>
     </row>
     <row r="80" s="11" customFormat="true" ht="37.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
       <c r="D80" s="8"/>
@@ -4847,7 +4868,7 @@
       <c r="J80" s="3"/>
     </row>
     <row r="81" s="11" customFormat="true" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="21" t="n">
+      <c r="A81" s="22" t="n">
         <v>36</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -4873,7 +4894,7 @@
       <c r="J81" s="3"/>
     </row>
     <row r="82" s="11" customFormat="true" ht="37.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="21"/>
+      <c r="A82" s="22"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="8"/>
@@ -4889,7 +4910,7 @@
       <c r="J82" s="3"/>
     </row>
     <row r="83" s="11" customFormat="true" ht="25.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="21"/>
+      <c r="A83" s="22"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="8"/>
@@ -4905,7 +4926,7 @@
       <c r="J83" s="3"/>
     </row>
     <row r="84" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="21"/>
+      <c r="A84" s="22"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="8"/>
@@ -4921,7 +4942,7 @@
       <c r="J84" s="3"/>
     </row>
     <row r="85" s="11" customFormat="true" ht="41.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="21"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="8"/>
@@ -4937,7 +4958,7 @@
       <c r="J85" s="3"/>
     </row>
     <row r="86" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="21" t="n">
+      <c r="A86" s="22" t="n">
         <v>37</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -4963,7 +4984,7 @@
       <c r="J86" s="3"/>
     </row>
     <row r="87" s="11" customFormat="true" ht="34.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="21"/>
+      <c r="A87" s="22"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="8"/>
@@ -4979,7 +5000,7 @@
       <c r="J87" s="3"/>
     </row>
     <row r="88" s="11" customFormat="true" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="21"/>
+      <c r="A88" s="22"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="8"/>
@@ -4987,7 +5008,7 @@
       <c r="F88" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G88" s="22" t="s">
+      <c r="G88" s="23" t="s">
         <v>202</v>
       </c>
       <c r="H88" s="2"/>
@@ -4995,7 +5016,7 @@
       <c r="J88" s="3"/>
     </row>
     <row r="89" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="13" t="n">
         <v>38</v>
       </c>
       <c r="B89" s="17" t="s">
@@ -5021,7 +5042,7 @@
       <c r="J89" s="3"/>
     </row>
     <row r="90" s="11" customFormat="true" ht="37.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1"/>
+      <c r="A90" s="13"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
       <c r="D90" s="8"/>
@@ -5037,7 +5058,7 @@
       <c r="J90" s="3"/>
     </row>
     <row r="91" s="11" customFormat="true" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1"/>
+      <c r="A91" s="13"/>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="8"/>
@@ -5053,7 +5074,7 @@
       <c r="J91" s="3"/>
     </row>
     <row r="92" s="11" customFormat="true" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1"/>
+      <c r="A92" s="13"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
       <c r="D92" s="8"/>
@@ -5069,7 +5090,7 @@
       <c r="J92" s="3"/>
     </row>
     <row r="93" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="13" t="n">
         <v>39</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -5095,7 +5116,7 @@
       <c r="J93" s="3"/>
     </row>
     <row r="94" s="11" customFormat="true" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1"/>
+      <c r="A94" s="13"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="8"/>
@@ -5113,7 +5134,7 @@
       <c r="J94" s="3"/>
     </row>
     <row r="95" s="11" customFormat="true" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1"/>
+      <c r="A95" s="13"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="8"/>
@@ -5129,7 +5150,7 @@
       <c r="J95" s="3"/>
     </row>
     <row r="96" s="11" customFormat="true" ht="33.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1"/>
+      <c r="A96" s="13"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="8"/>
@@ -5145,7 +5166,7 @@
       <c r="J96" s="3"/>
     </row>
     <row r="97" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="13" t="n">
         <v>40</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -5171,7 +5192,7 @@
       <c r="J97" s="3"/>
     </row>
     <row r="98" s="11" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1"/>
+      <c r="A98" s="13"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="8"/>
@@ -5187,7 +5208,7 @@
       <c r="J98" s="3"/>
     </row>
     <row r="99" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1"/>
+      <c r="A99" s="13"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="8"/>
@@ -5203,7 +5224,7 @@
       <c r="J99" s="3"/>
     </row>
     <row r="100" s="11" customFormat="true" ht="32.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1"/>
+      <c r="A100" s="13"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="8"/>
@@ -5219,7 +5240,7 @@
       <c r="J100" s="3"/>
     </row>
     <row r="101" s="11" customFormat="true" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1"/>
+      <c r="A101" s="13"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="8"/>
@@ -5235,7 +5256,7 @@
       <c r="J101" s="3"/>
     </row>
     <row r="102" s="11" customFormat="true" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="13" t="n">
         <v>41</v>
       </c>
       <c r="B102" s="17" t="s">
@@ -5261,7 +5282,7 @@
       <c r="J102" s="3"/>
     </row>
     <row r="103" s="11" customFormat="true" ht="48.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1"/>
+      <c r="A103" s="13"/>
       <c r="B103" s="17"/>
       <c r="C103" s="17"/>
       <c r="D103" s="8"/>
@@ -5277,7 +5298,7 @@
       <c r="J103" s="1"/>
     </row>
     <row r="104" s="11" customFormat="true" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1"/>
+      <c r="A104" s="13"/>
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
       <c r="D104" s="8"/>
@@ -5333,11 +5354,11 @@
       <c r="J106" s="3"/>
     </row>
     <row r="107" s="11" customFormat="true" ht="46.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="13" t="n">
         <v>43</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="C107" s="17" t="s">
         <v>171</v>
@@ -5346,29 +5367,29 @@
         <v>13</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
     </row>
     <row r="108" s="11" customFormat="true" ht="84.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1"/>
+      <c r="A108" s="13"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
       <c r="D108" s="8"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H108" s="2"/>
       <c r="I108" s="3"/>
@@ -5379,22 +5400,22 @@
         <v>44</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>179</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H109" s="2"/>
       <c r="I109" s="3"/>
@@ -5410,56 +5431,56 @@
         <v>181</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H110" s="2"/>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
     </row>
     <row r="111" s="11" customFormat="true" ht="23.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="13" t="n">
         <v>45</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
     </row>
     <row r="112" s="11" customFormat="true" ht="25.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1"/>
+      <c r="A112" s="13"/>
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
       <c r="D112" s="8"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
     </row>
     <row r="113" s="11" customFormat="true" ht="25.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1"/>
+      <c r="A113" s="13"/>
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
       <c r="D113" s="8"/>
@@ -5475,55 +5496,55 @@
       <c r="J113" s="3"/>
     </row>
     <row r="114" s="11" customFormat="true" ht="20.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1"/>
+      <c r="A114" s="13"/>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
       <c r="D114" s="8"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H114" s="2"/>
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
     </row>
     <row r="115" s="11" customFormat="true" ht="25.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1"/>
+      <c r="A115" s="13"/>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="8"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H115" s="2"/>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
     </row>
     <row r="116" s="11" customFormat="true" ht="38.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1"/>
+      <c r="A116" s="13"/>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
       <c r="D116" s="8"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
     </row>
     <row r="117" s="11" customFormat="true" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="13" t="n">
         <v>46</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -5536,36 +5557,36 @@
         <v>197</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
     </row>
     <row r="118" s="11" customFormat="true" ht="97.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1"/>
+      <c r="A118" s="13"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="8"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
     </row>
     <row r="119" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="13" t="n">
         <v>47</v>
       </c>
       <c r="B119" s="17" t="s">
@@ -5578,36 +5599,36 @@
         <v>197</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
     </row>
     <row r="120" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1"/>
+      <c r="A120" s="13"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
       <c r="D120" s="8"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
     </row>
     <row r="121" s="11" customFormat="true" ht="84.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1"/>
+      <c r="A121" s="13"/>
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
       <c r="D121" s="8"/>
@@ -5616,14 +5637,14 @@
         <v>201</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
     </row>
     <row r="122" s="11" customFormat="true" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="13" t="n">
         <v>48</v>
       </c>
       <c r="B122" s="17" t="s">
@@ -5636,36 +5657,36 @@
         <v>197</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
     </row>
     <row r="123" s="11" customFormat="true" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1"/>
+      <c r="A123" s="13"/>
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
       <c r="D123" s="8"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H123" s="2"/>
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
     </row>
     <row r="124" s="11" customFormat="true" ht="72.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1"/>
+      <c r="A124" s="13"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
       <c r="D124" s="8"/>
@@ -5674,63 +5695,63 @@
         <v>201</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H124" s="2"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
     </row>
     <row r="125" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="13" t="n">
         <v>49</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H125" s="2"/>
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
     </row>
     <row r="126" s="11" customFormat="true" ht="24.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1"/>
+      <c r="A126" s="13"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="8"/>
       <c r="E126" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H126" s="2"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
     </row>
     <row r="127" s="11" customFormat="true" ht="23.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1"/>
+      <c r="A127" s="13"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="8"/>
       <c r="E127" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>208</v>
@@ -5743,97 +5764,97 @@
       <c r="J127" s="3"/>
     </row>
     <row r="128" s="11" customFormat="true" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1"/>
+      <c r="A128" s="13"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="8"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H128" s="2"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
     </row>
     <row r="129" s="11" customFormat="true" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1"/>
+      <c r="A129" s="13"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="8"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
     </row>
     <row r="130" s="11" customFormat="true" ht="39.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1"/>
+      <c r="A130" s="13"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="8"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H130" s="2"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
     </row>
     <row r="131" s="11" customFormat="true" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="13" t="n">
         <v>50</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
     </row>
     <row r="132" s="11" customFormat="true" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1"/>
+      <c r="A132" s="13"/>
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="8"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H132" s="2"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
     </row>
     <row r="133" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1"/>
+      <c r="A133" s="13"/>
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="8"/>
@@ -5849,97 +5870,97 @@
       <c r="J133" s="3"/>
     </row>
     <row r="134" s="11" customFormat="true" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1"/>
+      <c r="A134" s="13"/>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
       <c r="D134" s="8"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H134" s="2"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
     </row>
     <row r="135" s="11" customFormat="true" ht="25.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1"/>
+      <c r="A135" s="13"/>
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
       <c r="D135" s="8"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H135" s="2"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
     </row>
     <row r="136" s="11" customFormat="true" ht="41.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="1"/>
+      <c r="A136" s="13"/>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
       <c r="D136" s="8"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
     </row>
     <row r="137" s="11" customFormat="true" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="13" t="n">
         <v>51</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D137" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H137" s="2"/>
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
     </row>
     <row r="138" s="11" customFormat="true" ht="24.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1"/>
+      <c r="A138" s="13"/>
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
       <c r="D138" s="8"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
     </row>
     <row r="139" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="1"/>
+      <c r="A139" s="13"/>
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
       <c r="D139" s="8"/>
@@ -5955,97 +5976,97 @@
       <c r="J139" s="3"/>
     </row>
     <row r="140" s="11" customFormat="true" ht="20.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1"/>
+      <c r="A140" s="13"/>
       <c r="B140" s="17"/>
       <c r="C140" s="17"/>
       <c r="D140" s="8"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H140" s="2"/>
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
     </row>
     <row r="141" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1"/>
+      <c r="A141" s="13"/>
       <c r="B141" s="17"/>
       <c r="C141" s="17"/>
       <c r="D141" s="8"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H141" s="2"/>
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
     </row>
     <row r="142" s="11" customFormat="true" ht="38.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="1"/>
+      <c r="A142" s="13"/>
       <c r="B142" s="17"/>
       <c r="C142" s="17"/>
       <c r="D142" s="8"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
     </row>
     <row r="143" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="13" t="n">
         <v>52</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D143" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
     </row>
     <row r="144" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1"/>
+      <c r="A144" s="13"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="8"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
     </row>
     <row r="145" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1"/>
+      <c r="A145" s="13"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="8"/>
@@ -6061,48 +6082,48 @@
       <c r="J145" s="3"/>
     </row>
     <row r="146" s="11" customFormat="true" ht="22.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1"/>
+      <c r="A146" s="13"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="8"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
     </row>
     <row r="147" s="11" customFormat="true" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1"/>
+      <c r="A147" s="13"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="8"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
     </row>
     <row r="148" s="11" customFormat="true" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1"/>
+      <c r="A148" s="13"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="8"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" s="3"/>
@@ -6110,7 +6131,7 @@
     </row>
     <row r="149" s="11" customFormat="true" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -6127,28 +6148,28 @@
         <v>53</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I150" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J150" s="3"/>
     </row>
@@ -6159,10 +6180,10 @@
       <c r="D151" s="8"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H151" s="2"/>
       <c r="I151" s="16"/>
@@ -6175,10 +6196,10 @@
       <c r="D152" s="8"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H152" s="2"/>
       <c r="I152" s="16"/>
@@ -6191,10 +6212,10 @@
       <c r="D153" s="8"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H153" s="2"/>
       <c r="I153" s="16"/>
@@ -6207,10 +6228,10 @@
       <c r="D154" s="8"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H154" s="2"/>
       <c r="I154" s="16"/>
@@ -6223,10 +6244,10 @@
       <c r="D155" s="8"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="16"/>
@@ -6237,22 +6258,22 @@
         <v>54</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C156" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="3"/>
@@ -6263,22 +6284,22 @@
         <v>55</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H157" s="2"/>
       <c r="I157" s="3"/>
@@ -6291,10 +6312,10 @@
       <c r="D158" s="8"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H158" s="2"/>
       <c r="I158" s="3"/>
@@ -6307,10 +6328,10 @@
       <c r="D159" s="8"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H159" s="2"/>
       <c r="I159" s="3"/>
@@ -6323,10 +6344,10 @@
       <c r="D160" s="8"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H160" s="2"/>
       <c r="I160" s="3"/>
@@ -6339,10 +6360,10 @@
       <c r="D161" s="8"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H161" s="2"/>
       <c r="I161" s="3"/>
@@ -6353,22 +6374,22 @@
         <v>56</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H162" s="2"/>
       <c r="I162" s="3"/>
@@ -6381,10 +6402,10 @@
       <c r="D163" s="8"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H163" s="2"/>
       <c r="I163" s="3"/>
@@ -6397,10 +6418,10 @@
       <c r="D164" s="8"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H164" s="2"/>
       <c r="I164" s="3"/>
@@ -6413,10 +6434,10 @@
       <c r="D165" s="8"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H165" s="2"/>
       <c r="I165" s="3"/>
@@ -6429,10 +6450,10 @@
       <c r="D166" s="8"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H166" s="2"/>
       <c r="I166" s="3"/>
@@ -6445,10 +6466,10 @@
       <c r="D167" s="8"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H167" s="2"/>
       <c r="I167" s="3"/>
@@ -6459,22 +6480,22 @@
         <v>57</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D168" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="3"/>
@@ -6487,10 +6508,10 @@
       <c r="D169" s="8"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="3"/>
@@ -6503,10 +6524,10 @@
       <c r="D170" s="8"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H170" s="2"/>
       <c r="I170" s="3"/>
@@ -6519,10 +6540,10 @@
       <c r="D171" s="8"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H171" s="2"/>
       <c r="I171" s="3"/>
@@ -6535,10 +6556,10 @@
       <c r="D172" s="8"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H172" s="2"/>
       <c r="I172" s="3"/>
@@ -6549,22 +6570,22 @@
         <v>58</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D173" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H173" s="2"/>
       <c r="I173" s="3"/>
@@ -6577,10 +6598,10 @@
       <c r="D174" s="8"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H174" s="2"/>
       <c r="I174" s="3"/>
@@ -6593,10 +6614,10 @@
       <c r="D175" s="8"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H175" s="2"/>
       <c r="I175" s="3"/>
@@ -6609,10 +6630,10 @@
       <c r="D176" s="8"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H176" s="2"/>
       <c r="I176" s="3"/>
@@ -6625,10 +6646,10 @@
       <c r="D177" s="8"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H177" s="2"/>
       <c r="I177" s="3"/>
@@ -6639,22 +6660,22 @@
         <v>59</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D178" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H178" s="2"/>
       <c r="I178" s="3"/>
@@ -6667,10 +6688,10 @@
       <c r="D179" s="8"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H179" s="2"/>
       <c r="I179" s="3"/>
@@ -6683,10 +6704,10 @@
       <c r="D180" s="8"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H180" s="2"/>
       <c r="I180" s="3"/>
@@ -6699,10 +6720,10 @@
       <c r="D181" s="8"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H181" s="2"/>
       <c r="I181" s="3"/>
@@ -6715,10 +6736,10 @@
       <c r="D182" s="8"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H182" s="2"/>
       <c r="I182" s="3"/>
@@ -6729,22 +6750,22 @@
         <v>60</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D183" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H183" s="2"/>
       <c r="I183" s="3"/>
@@ -6757,10 +6778,10 @@
       <c r="D184" s="8"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H184" s="2"/>
       <c r="I184" s="3"/>
@@ -6773,10 +6794,10 @@
       <c r="D185" s="8"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H185" s="2"/>
       <c r="I185" s="3"/>
@@ -6789,10 +6810,10 @@
       <c r="D186" s="8"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H186" s="2"/>
       <c r="I186" s="3"/>
@@ -6805,10 +6826,10 @@
       <c r="D187" s="8"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H187" s="2"/>
       <c r="I187" s="3"/>
@@ -6819,22 +6840,22 @@
         <v>61</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H188" s="2"/>
       <c r="I188" s="3"/>
@@ -6847,10 +6868,10 @@
       <c r="D189" s="8"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H189" s="2"/>
       <c r="I189" s="3"/>
@@ -6858,7 +6879,7 @@
     </row>
     <row r="190" s="11" customFormat="true" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B190" s="20"/>
       <c r="C190" s="20"/>
@@ -6871,370 +6892,370 @@
       <c r="J190" s="20"/>
     </row>
     <row r="191" s="11" customFormat="true" ht="22.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="13" t="n">
         <v>62</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D191" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H191" s="2"/>
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
     </row>
     <row r="192" s="11" customFormat="true" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1"/>
+      <c r="A192" s="13"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="8"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H192" s="2"/>
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
     </row>
     <row r="193" s="11" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1"/>
+      <c r="A193" s="13"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="8"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H193" s="2"/>
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
     </row>
     <row r="194" s="11" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1"/>
+      <c r="A194" s="13"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="8"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H194" s="2"/>
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
     </row>
     <row r="195" s="11" customFormat="true" ht="43.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="13" t="n">
         <v>63</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E195" s="22" t="s">
-        <v>327</v>
+      <c r="E195" s="23" t="s">
+        <v>328</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H195" s="2"/>
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
     </row>
     <row r="196" s="11" customFormat="true" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1"/>
+      <c r="A196" s="13"/>
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
       <c r="D196" s="8"/>
-      <c r="E196" s="22"/>
+      <c r="E196" s="23"/>
       <c r="F196" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H196" s="2"/>
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
     </row>
     <row r="197" s="11" customFormat="true" ht="38.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1"/>
+      <c r="A197" s="13"/>
       <c r="B197" s="17"/>
       <c r="C197" s="17"/>
       <c r="D197" s="8"/>
-      <c r="E197" s="22"/>
+      <c r="E197" s="23"/>
       <c r="F197" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H197" s="2"/>
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
     </row>
     <row r="198" s="11" customFormat="true" ht="58.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1"/>
+      <c r="A198" s="13"/>
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
       <c r="D198" s="8"/>
-      <c r="E198" s="22"/>
+      <c r="E198" s="23"/>
       <c r="F198" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H198" s="2"/>
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
     </row>
     <row r="199" s="11" customFormat="true" ht="40.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="13" t="n">
         <v>64</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D199" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E199" s="22" t="s">
-        <v>334</v>
+      <c r="E199" s="23" t="s">
+        <v>335</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H199" s="2"/>
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
     </row>
     <row r="200" s="11" customFormat="true" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="1"/>
+      <c r="A200" s="13"/>
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
       <c r="D200" s="8"/>
-      <c r="E200" s="22"/>
+      <c r="E200" s="23"/>
       <c r="F200" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H200" s="2"/>
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
     </row>
     <row r="201" s="11" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1"/>
+      <c r="A201" s="13"/>
       <c r="B201" s="17"/>
       <c r="C201" s="17"/>
       <c r="D201" s="8"/>
-      <c r="E201" s="22"/>
+      <c r="E201" s="23"/>
       <c r="F201" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H201" s="2"/>
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
     </row>
     <row r="202" s="11" customFormat="true" ht="40.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1"/>
+      <c r="A202" s="13"/>
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
       <c r="D202" s="8"/>
-      <c r="E202" s="22"/>
+      <c r="E202" s="23"/>
       <c r="F202" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H202" s="2"/>
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
     </row>
     <row r="203" s="11" customFormat="true" ht="28.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="13" t="n">
         <v>65</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D203" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H203" s="2"/>
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
     </row>
     <row r="204" s="11" customFormat="true" ht="35.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1"/>
+      <c r="A204" s="13"/>
       <c r="B204" s="17"/>
       <c r="C204" s="17"/>
       <c r="D204" s="8"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H204" s="2"/>
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
     </row>
     <row r="205" s="11" customFormat="true" ht="65.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="1"/>
+      <c r="A205" s="13"/>
       <c r="B205" s="17"/>
       <c r="C205" s="17"/>
       <c r="D205" s="8"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H205" s="2"/>
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
     </row>
     <row r="206" s="11" customFormat="true" ht="39.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="1"/>
+      <c r="A206" s="13"/>
       <c r="B206" s="17"/>
       <c r="C206" s="17"/>
       <c r="D206" s="8"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H206" s="2"/>
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
     </row>
     <row r="207" s="11" customFormat="true" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="13" t="n">
         <v>66</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C207" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D207" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H207" s="2"/>
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
     </row>
     <row r="208" s="11" customFormat="true" ht="53.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="1"/>
+      <c r="A208" s="13"/>
       <c r="B208" s="17"/>
       <c r="C208" s="17"/>
       <c r="D208" s="8"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H208" s="2"/>
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
     </row>
     <row r="209" s="11" customFormat="true" ht="54.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="1"/>
+      <c r="A209" s="13"/>
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
       <c r="D209" s="8"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H209" s="2"/>
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
     </row>
     <row r="210" s="11" customFormat="true" ht="40.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="1"/>
+      <c r="A210" s="13"/>
       <c r="B210" s="17"/>
       <c r="C210" s="17"/>
       <c r="D210" s="8"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H210" s="2"/>
       <c r="I210" s="3"/>
@@ -7245,22 +7266,22 @@
         <v>67</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C211" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D211" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H211" s="2"/>
       <c r="I211" s="3"/>
@@ -7273,10 +7294,10 @@
       <c r="D212" s="8"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H212" s="2"/>
       <c r="I212" s="3"/>
@@ -7289,407 +7310,407 @@
       <c r="D213" s="8"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H213" s="2"/>
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
     </row>
     <row r="214" s="11" customFormat="true" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="13" t="n">
         <v>68</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D214" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H214" s="2"/>
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
     </row>
     <row r="215" s="11" customFormat="true" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="1"/>
+      <c r="A215" s="13"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="8"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H215" s="2"/>
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
     </row>
     <row r="216" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="1"/>
+      <c r="A216" s="13"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="8"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H216" s="2"/>
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
     </row>
     <row r="217" s="11" customFormat="true" ht="40.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="1"/>
+      <c r="A217" s="13"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="8"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H217" s="2"/>
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
     </row>
     <row r="218" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="13" t="n">
         <v>69</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D218" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H218" s="2"/>
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
     </row>
     <row r="219" s="11" customFormat="true" ht="31.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="1"/>
+      <c r="A219" s="13"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="8"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H219" s="2"/>
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
     </row>
     <row r="220" s="11" customFormat="true" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="1"/>
+      <c r="A220" s="13"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="8"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H220" s="2"/>
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
     </row>
     <row r="221" s="11" customFormat="true" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="1"/>
+      <c r="A221" s="13"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
       <c r="D221" s="8"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H221" s="2"/>
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
     </row>
     <row r="222" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="13" t="n">
         <v>70</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H222" s="2"/>
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
     </row>
     <row r="223" s="11" customFormat="true" ht="44.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="1"/>
+      <c r="A223" s="13"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
       <c r="D223" s="8"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H223" s="2"/>
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
     </row>
     <row r="224" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="1"/>
+      <c r="A224" s="13"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
       <c r="D224" s="8"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H224" s="2"/>
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
     </row>
     <row r="225" s="11" customFormat="true" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="1"/>
+      <c r="A225" s="13"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
       <c r="D225" s="8"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H225" s="2"/>
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
     </row>
     <row r="226" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="13" t="n">
         <v>71</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H226" s="2"/>
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
     </row>
     <row r="227" s="11" customFormat="true" ht="48.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="1"/>
+      <c r="A227" s="13"/>
       <c r="B227" s="17"/>
       <c r="C227" s="17"/>
       <c r="D227" s="8"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H227" s="2"/>
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
     </row>
     <row r="228" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="1"/>
+      <c r="A228" s="13"/>
       <c r="B228" s="17"/>
       <c r="C228" s="17"/>
       <c r="D228" s="8"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H228" s="2"/>
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
     </row>
     <row r="229" s="11" customFormat="true" ht="38.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="1"/>
+      <c r="A229" s="13"/>
       <c r="B229" s="17"/>
       <c r="C229" s="17"/>
       <c r="D229" s="8"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H229" s="2"/>
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
     </row>
     <row r="230" s="11" customFormat="true" ht="28.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="13" t="n">
         <v>72</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D230" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H230" s="2"/>
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
     </row>
     <row r="231" s="11" customFormat="true" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1"/>
+      <c r="A231" s="13"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
       <c r="D231" s="8"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H231" s="2"/>
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
     </row>
     <row r="232" s="11" customFormat="true" ht="33.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="1"/>
+      <c r="A232" s="13"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
       <c r="D232" s="8"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H232" s="2"/>
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
     </row>
     <row r="233" s="11" customFormat="true" ht="44.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="1"/>
+      <c r="A233" s="13"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
       <c r="D233" s="8"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H233" s="2"/>
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
     </row>
     <row r="234" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="1"/>
+      <c r="A234" s="13"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
       <c r="D234" s="8"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H234" s="2"/>
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
     </row>
     <row r="235" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="13" t="n">
         <v>73</v>
       </c>
-      <c r="B235" s="23" t="s">
-        <v>371</v>
+      <c r="B235" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>372</v>
@@ -7698,22 +7719,22 @@
         <v>13</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H235" s="2"/>
       <c r="I235" s="1"/>
       <c r="J235" s="3"/>
     </row>
     <row r="236" s="11" customFormat="true" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="1"/>
-      <c r="B236" s="23"/>
-      <c r="C236" s="23"/>
+      <c r="A236" s="13"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
       <c r="D236" s="8"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2" t="s">
@@ -9494,7 +9515,7 @@
       <c r="K11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="24" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -9518,7 +9539,7 @@
       <c r="K12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
+      <c r="A13" s="24"/>
       <c r="D13" s="8"/>
       <c r="F13" s="2" t="s">
         <v>45</v>
@@ -9529,7 +9550,7 @@
       <c r="K13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="26.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13"/>
+      <c r="A14" s="24"/>
       <c r="D14" s="8"/>
       <c r="F14" s="2" t="s">
         <v>47</v>
@@ -9540,7 +9561,7 @@
       <c r="K14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="n">
+      <c r="A15" s="24" t="n">
         <v>6</v>
       </c>
       <c r="B15" s="14" t="s">
@@ -9563,7 +9584,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="8"/>
@@ -9575,7 +9596,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="8"/>
@@ -9587,7 +9608,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="24" t="n">
         <v>7</v>
       </c>
       <c r="B18" s="14" t="s">
@@ -9610,7 +9631,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="8"/>
@@ -9622,7 +9643,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="52" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="8"/>
@@ -9634,7 +9655,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="n">
+      <c r="A21" s="24" t="n">
         <v>8</v>
       </c>
       <c r="B21" s="14" t="s">
@@ -9658,7 +9679,7 @@
       <c r="I21" s="16"/>
     </row>
     <row r="22" customFormat="false" ht="33.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="8"/>
@@ -9671,7 +9692,7 @@
       <c r="I22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="48.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="8"/>
@@ -9684,7 +9705,7 @@
       <c r="I23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="n">
+      <c r="A24" s="24" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -9707,7 +9728,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="38.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
+      <c r="A25" s="24"/>
       <c r="C25" s="15"/>
       <c r="D25" s="8"/>
       <c r="F25" s="2" t="s">
@@ -9718,7 +9739,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="54.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
+      <c r="A26" s="24"/>
       <c r="C26" s="15"/>
       <c r="D26" s="8"/>
       <c r="F26" s="2" t="s">
@@ -9729,7 +9750,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="n">
+      <c r="A27" s="24" t="n">
         <v>10</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -9752,7 +9773,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
+      <c r="A28" s="24"/>
       <c r="D28" s="8"/>
       <c r="F28" s="2" t="s">
         <v>79</v>
@@ -9762,7 +9783,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="54.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
+      <c r="A29" s="24"/>
       <c r="D29" s="8"/>
       <c r="F29" s="2" t="s">
         <v>47</v>
@@ -9772,7 +9793,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="n">
+      <c r="A30" s="24" t="n">
         <v>11</v>
       </c>
       <c r="B30" s="17" t="s">
@@ -9801,7 +9822,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="8"/>
@@ -9814,7 +9835,7 @@
       <c r="I31" s="18"/>
     </row>
     <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="8"/>
@@ -9827,7 +9848,7 @@
       <c r="I32" s="18"/>
     </row>
     <row r="33" customFormat="false" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="n">
+      <c r="A33" s="24" t="n">
         <v>12</v>
       </c>
       <c r="B33" s="17" t="s">
@@ -9853,7 +9874,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13"/>
+      <c r="A34" s="24"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="8"/>
@@ -9865,7 +9886,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13"/>
+      <c r="A35" s="24"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="8"/>
@@ -10118,7 +10139,7 @@
       <c r="J50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="24.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="n">
+      <c r="A51" s="24" t="n">
         <v>17</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -10141,7 +10162,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13"/>
+      <c r="A52" s="24"/>
       <c r="D52" s="8"/>
       <c r="F52" s="2" t="s">
         <v>119</v>
@@ -10151,7 +10172,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="n">
+      <c r="A53" s="24" t="n">
         <v>18</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -10174,7 +10195,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="24.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13"/>
+      <c r="A54" s="24"/>
       <c r="D54" s="8"/>
       <c r="F54" s="2" t="s">
         <v>124</v>
@@ -10414,7 +10435,7 @@
       <c r="K66" s="11"/>
     </row>
     <row r="67" customFormat="false" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="21" t="n">
+      <c r="A67" s="25" t="n">
         <v>25</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -10438,7 +10459,7 @@
       <c r="K67" s="11"/>
     </row>
     <row r="68" customFormat="false" ht="37.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21"/>
+      <c r="A68" s="25"/>
       <c r="D68" s="8"/>
       <c r="F68" s="2" t="s">
         <v>188</v>
@@ -10449,7 +10470,7 @@
       <c r="K68" s="11"/>
     </row>
     <row r="69" customFormat="false" ht="25.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21"/>
+      <c r="A69" s="25"/>
       <c r="D69" s="8"/>
       <c r="F69" s="2" t="s">
         <v>190</v>
@@ -10460,7 +10481,7 @@
       <c r="K69" s="11"/>
     </row>
     <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="21"/>
+      <c r="A70" s="25"/>
       <c r="D70" s="8"/>
       <c r="F70" s="2" t="s">
         <v>192</v>
@@ -10471,7 +10492,7 @@
       <c r="K70" s="11"/>
     </row>
     <row r="71" customFormat="false" ht="41.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="21"/>
+      <c r="A71" s="25"/>
       <c r="D71" s="8"/>
       <c r="F71" s="2" t="s">
         <v>194</v>
@@ -10482,7 +10503,7 @@
       <c r="K71" s="11"/>
     </row>
     <row r="72" customFormat="false" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="21" t="n">
+      <c r="A72" s="25" t="n">
         <v>26</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -10506,7 +10527,7 @@
       <c r="K72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="34.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21"/>
+      <c r="A73" s="25"/>
       <c r="D73" s="8"/>
       <c r="F73" s="2" t="s">
         <v>188</v>
@@ -10517,12 +10538,12 @@
       <c r="K73" s="11"/>
     </row>
     <row r="74" customFormat="false" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="21"/>
+      <c r="A74" s="25"/>
       <c r="D74" s="8"/>
       <c r="F74" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G74" s="22" t="s">
+      <c r="G74" s="23" t="s">
         <v>202</v>
       </c>
       <c r="K74" s="11"/>
@@ -10814,13 +10835,13 @@
         <v>13</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K93" s="11"/>
     </row>
@@ -10829,10 +10850,10 @@
       <c r="C94" s="17"/>
       <c r="D94" s="8"/>
       <c r="F94" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K94" s="11"/>
     </row>
@@ -10841,22 +10862,22 @@
         <v>33</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>179</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K95" s="11"/>
     </row>
@@ -10868,7 +10889,7 @@
         <v>181</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K96" s="11"/>
     </row>
@@ -10877,22 +10898,22 @@
         <v>34</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K97" s="11"/>
     </row>
@@ -10901,10 +10922,10 @@
       <c r="C98" s="17"/>
       <c r="D98" s="8"/>
       <c r="F98" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K98" s="11"/>
     </row>
@@ -10925,10 +10946,10 @@
       <c r="C100" s="17"/>
       <c r="D100" s="8"/>
       <c r="F100" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K100" s="11"/>
     </row>
@@ -10937,10 +10958,10 @@
       <c r="C101" s="17"/>
       <c r="D101" s="8"/>
       <c r="F101" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K101" s="11"/>
     </row>
@@ -10949,10 +10970,10 @@
       <c r="C102" s="17"/>
       <c r="D102" s="8"/>
       <c r="F102" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K102" s="11"/>
     </row>
@@ -10970,23 +10991,23 @@
         <v>197</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K103" s="11"/>
     </row>
     <row r="104" customFormat="false" ht="97.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D104" s="8"/>
       <c r="F104" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K104" s="11"/>
     </row>
@@ -11004,13 +11025,13 @@
         <v>197</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K105" s="11"/>
     </row>
@@ -11019,10 +11040,10 @@
       <c r="C106" s="17"/>
       <c r="D106" s="8"/>
       <c r="F106" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K106" s="11"/>
     </row>
@@ -11034,7 +11055,7 @@
         <v>201</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K107" s="11"/>
     </row>
@@ -11052,13 +11073,13 @@
         <v>197</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K108" s="11"/>
     </row>
@@ -11067,10 +11088,10 @@
       <c r="C109" s="17"/>
       <c r="D109" s="8"/>
       <c r="F109" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K109" s="11"/>
     </row>
@@ -11082,7 +11103,7 @@
         <v>201</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K110" s="11"/>
     </row>
@@ -11091,42 +11112,42 @@
         <v>38</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K111" s="11"/>
     </row>
     <row r="112" customFormat="false" ht="24.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D112" s="8"/>
       <c r="E112" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K112" s="11"/>
     </row>
     <row r="113" customFormat="false" ht="23.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D113" s="8"/>
       <c r="E113" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>208</v>
@@ -11139,30 +11160,30 @@
     <row r="114" customFormat="false" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D114" s="8"/>
       <c r="F114" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K114" s="11"/>
     </row>
     <row r="115" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D115" s="8"/>
       <c r="F115" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K115" s="11"/>
     </row>
     <row r="116" customFormat="false" ht="39.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D116" s="8"/>
       <c r="F116" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K116" s="11"/>
     </row>
@@ -11171,22 +11192,22 @@
         <v>39</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K117" s="11"/>
     </row>
@@ -11195,10 +11216,10 @@
       <c r="C118" s="17"/>
       <c r="D118" s="8"/>
       <c r="F118" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K118" s="11"/>
     </row>
@@ -11219,10 +11240,10 @@
       <c r="C120" s="17"/>
       <c r="D120" s="8"/>
       <c r="F120" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K120" s="11"/>
     </row>
@@ -11231,10 +11252,10 @@
       <c r="C121" s="17"/>
       <c r="D121" s="8"/>
       <c r="F121" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K121" s="11"/>
     </row>
@@ -11243,10 +11264,10 @@
       <c r="C122" s="17"/>
       <c r="D122" s="8"/>
       <c r="F122" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K122" s="11"/>
     </row>
@@ -11255,22 +11276,22 @@
         <v>40</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K123" s="11"/>
     </row>
@@ -11279,10 +11300,10 @@
       <c r="C124" s="17"/>
       <c r="D124" s="8"/>
       <c r="F124" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K124" s="11"/>
     </row>
@@ -11303,10 +11324,10 @@
       <c r="C126" s="17"/>
       <c r="D126" s="8"/>
       <c r="F126" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K126" s="11"/>
     </row>
@@ -11315,10 +11336,10 @@
       <c r="C127" s="17"/>
       <c r="D127" s="8"/>
       <c r="F127" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K127" s="11"/>
     </row>
@@ -11327,10 +11348,10 @@
       <c r="C128" s="17"/>
       <c r="D128" s="8"/>
       <c r="F128" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K128" s="11"/>
     </row>
@@ -11339,32 +11360,32 @@
         <v>41</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K129" s="11"/>
     </row>
     <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D130" s="8"/>
       <c r="F130" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K130" s="11"/>
     </row>
@@ -11381,36 +11402,36 @@
     <row r="132" customFormat="false" ht="22.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D132" s="8"/>
       <c r="F132" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K132" s="11"/>
     </row>
     <row r="133" customFormat="false" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D133" s="8"/>
       <c r="F133" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K133" s="11"/>
     </row>
     <row r="134" customFormat="false" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D134" s="8"/>
       <c r="F134" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K134" s="11"/>
     </row>
     <row r="135" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -11428,28 +11449,28 @@
         <v>42</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D136" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I136" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K136" s="11"/>
     </row>
@@ -11458,10 +11479,10 @@
       <c r="C137" s="17"/>
       <c r="D137" s="8"/>
       <c r="F137" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I137" s="16"/>
       <c r="K137" s="11"/>
@@ -11474,7 +11495,7 @@
         <v>493</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I138" s="16"/>
       <c r="K138" s="11"/>
@@ -11487,7 +11508,7 @@
         <v>494</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I139" s="16"/>
       <c r="K139" s="11"/>
@@ -11497,10 +11518,10 @@
       <c r="C140" s="17"/>
       <c r="D140" s="8"/>
       <c r="F140" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I140" s="16"/>
       <c r="K140" s="11"/>
@@ -11510,10 +11531,10 @@
       <c r="C141" s="17"/>
       <c r="D141" s="8"/>
       <c r="F141" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I141" s="16"/>
       <c r="K141" s="11"/>
@@ -11532,13 +11553,13 @@
         <v>13</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K142" s="11"/>
     </row>
@@ -11556,13 +11577,13 @@
         <v>197</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K143" s="11"/>
     </row>
@@ -11574,7 +11595,7 @@
         <v>498</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K144" s="11"/>
     </row>
@@ -11595,10 +11616,10 @@
       <c r="C146" s="17"/>
       <c r="D146" s="8"/>
       <c r="F146" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K146" s="11"/>
     </row>
@@ -11607,10 +11628,10 @@
       <c r="C147" s="17"/>
       <c r="D147" s="8"/>
       <c r="F147" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K147" s="11"/>
     </row>
@@ -11628,13 +11649,13 @@
         <v>197</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K148" s="11"/>
     </row>
@@ -11643,10 +11664,10 @@
       <c r="C149" s="17"/>
       <c r="D149" s="8"/>
       <c r="F149" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K149" s="11"/>
     </row>
@@ -11658,7 +11679,7 @@
         <v>493</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K150" s="11"/>
     </row>
@@ -11670,7 +11691,7 @@
         <v>494</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K151" s="11"/>
     </row>
@@ -11679,10 +11700,10 @@
       <c r="C152" s="17"/>
       <c r="D152" s="8"/>
       <c r="F152" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K152" s="11"/>
     </row>
@@ -11691,10 +11712,10 @@
       <c r="C153" s="17"/>
       <c r="D153" s="8"/>
       <c r="F153" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K153" s="11"/>
     </row>
@@ -11712,13 +11733,13 @@
         <v>197</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K154" s="11"/>
     </row>
@@ -11730,7 +11751,7 @@
         <v>498</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K155" s="11"/>
     </row>
@@ -11742,7 +11763,7 @@
         <v>499</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K156" s="11"/>
     </row>
@@ -11751,10 +11772,10 @@
       <c r="C157" s="17"/>
       <c r="D157" s="8"/>
       <c r="F157" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K157" s="11"/>
     </row>
@@ -11763,10 +11784,10 @@
       <c r="C158" s="17"/>
       <c r="D158" s="8"/>
       <c r="F158" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K158" s="11"/>
     </row>
@@ -11784,23 +11805,23 @@
         <v>197</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K159" s="11"/>
     </row>
     <row r="160" customFormat="false" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D160" s="8"/>
       <c r="F160" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K160" s="11"/>
     </row>
@@ -11810,27 +11831,27 @@
         <v>499</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K161" s="11"/>
     </row>
     <row r="162" customFormat="false" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D162" s="8"/>
       <c r="F162" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K162" s="11"/>
     </row>
     <row r="163" customFormat="false" ht="69.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D163" s="8"/>
       <c r="F163" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K163" s="11"/>
     </row>
@@ -11848,23 +11869,23 @@
         <v>197</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K164" s="11"/>
     </row>
     <row r="165" customFormat="false" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D165" s="8"/>
       <c r="F165" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K165" s="11"/>
     </row>
@@ -11874,27 +11895,27 @@
         <v>493</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K166" s="11"/>
     </row>
     <row r="167" customFormat="false" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D167" s="8"/>
       <c r="F167" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K167" s="11"/>
     </row>
     <row r="168" customFormat="false" ht="62.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D168" s="8"/>
       <c r="F168" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K168" s="11"/>
     </row>
@@ -11903,32 +11924,32 @@
         <v>49</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D169" s="8" t="s">
         <v>197</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K169" s="11"/>
     </row>
     <row r="170" customFormat="false" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D170" s="8"/>
       <c r="F170" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K170" s="11"/>
     </row>
@@ -11938,7 +11959,7 @@
         <v>493</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K171" s="11"/>
     </row>
@@ -11948,17 +11969,17 @@
         <v>494</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K172" s="11"/>
     </row>
     <row r="173" customFormat="false" ht="57.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D173" s="8"/>
       <c r="F173" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K173" s="11"/>
     </row>
@@ -11967,22 +11988,22 @@
         <v>50</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D174" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K174" s="11"/>
     </row>
@@ -11990,16 +12011,16 @@
       <c r="B175" s="17"/>
       <c r="D175" s="8"/>
       <c r="F175" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K175" s="11"/>
     </row>
     <row r="176" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B176" s="20"/>
       <c r="C176" s="20"/>
@@ -12017,52 +12038,52 @@
         <v>51</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K177" s="11"/>
     </row>
     <row r="178" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D178" s="8"/>
       <c r="F178" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K178" s="11"/>
     </row>
     <row r="179" customFormat="false" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D179" s="8"/>
       <c r="F179" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K179" s="11"/>
     </row>
     <row r="180" customFormat="false" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D180" s="8"/>
       <c r="F180" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K180" s="11"/>
     </row>
@@ -12071,22 +12092,22 @@
         <v>52</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D181" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E181" s="22" t="s">
-        <v>327</v>
+      <c r="E181" s="23" t="s">
+        <v>328</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K181" s="11"/>
     </row>
@@ -12094,12 +12115,12 @@
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
       <c r="D182" s="8"/>
-      <c r="E182" s="22"/>
+      <c r="E182" s="23"/>
       <c r="F182" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K182" s="11"/>
     </row>
@@ -12107,12 +12128,12 @@
       <c r="B183" s="17"/>
       <c r="C183" s="17"/>
       <c r="D183" s="8"/>
-      <c r="E183" s="22"/>
+      <c r="E183" s="23"/>
       <c r="F183" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K183" s="11"/>
     </row>
@@ -12120,12 +12141,12 @@
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
       <c r="D184" s="8"/>
-      <c r="E184" s="22"/>
+      <c r="E184" s="23"/>
       <c r="F184" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K184" s="11"/>
     </row>
@@ -12134,22 +12155,22 @@
         <v>53</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D185" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E185" s="22" t="s">
-        <v>334</v>
+      <c r="E185" s="23" t="s">
+        <v>335</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K185" s="11"/>
     </row>
@@ -12157,12 +12178,12 @@
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
       <c r="D186" s="8"/>
-      <c r="E186" s="22"/>
+      <c r="E186" s="23"/>
       <c r="F186" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K186" s="11"/>
     </row>
@@ -12170,12 +12191,12 @@
       <c r="B187" s="17"/>
       <c r="C187" s="17"/>
       <c r="D187" s="8"/>
-      <c r="E187" s="22"/>
+      <c r="E187" s="23"/>
       <c r="F187" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K187" s="11"/>
     </row>
@@ -12183,12 +12204,12 @@
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
       <c r="D188" s="8"/>
-      <c r="E188" s="22"/>
+      <c r="E188" s="23"/>
       <c r="F188" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K188" s="11"/>
     </row>
@@ -12197,22 +12218,22 @@
         <v>54</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D189" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K189" s="11"/>
     </row>
@@ -12221,10 +12242,10 @@
       <c r="C190" s="17"/>
       <c r="D190" s="8"/>
       <c r="F190" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K190" s="11"/>
     </row>
@@ -12233,10 +12254,10 @@
       <c r="C191" s="17"/>
       <c r="D191" s="8"/>
       <c r="F191" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K191" s="11"/>
     </row>
@@ -12245,10 +12266,10 @@
       <c r="C192" s="17"/>
       <c r="D192" s="8"/>
       <c r="F192" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K192" s="11"/>
     </row>
@@ -12257,22 +12278,22 @@
         <v>55</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C193" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K193" s="11"/>
     </row>
@@ -12281,10 +12302,10 @@
       <c r="C194" s="17"/>
       <c r="D194" s="8"/>
       <c r="F194" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K194" s="11"/>
     </row>
@@ -12293,10 +12314,10 @@
       <c r="C195" s="17"/>
       <c r="D195" s="8"/>
       <c r="F195" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K195" s="11"/>
     </row>
@@ -12305,10 +12326,10 @@
       <c r="C196" s="17"/>
       <c r="D196" s="8"/>
       <c r="F196" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K196" s="11"/>
     </row>
@@ -12317,42 +12338,42 @@
         <v>56</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C197" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D198" s="8"/>
       <c r="F198" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="44.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D199" s="8"/>
       <c r="F199" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K199" s="11"/>
     </row>
@@ -12361,52 +12382,52 @@
         <v>57</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D200" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D201" s="8"/>
       <c r="F201" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K201" s="11"/>
     </row>
     <row r="202" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D202" s="8"/>
       <c r="F202" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K202" s="11"/>
     </row>
     <row r="203" customFormat="false" ht="40.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D203" s="8"/>
       <c r="F203" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K203" s="11"/>
     </row>
@@ -12415,52 +12436,52 @@
         <v>58</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D204" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="31.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D205" s="8"/>
       <c r="F205" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K205" s="11"/>
     </row>
     <row r="206" customFormat="false" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D206" s="8"/>
       <c r="F206" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K206" s="11"/>
     </row>
     <row r="207" customFormat="false" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D207" s="8"/>
       <c r="F207" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K207" s="11"/>
     </row>
@@ -12469,52 +12490,52 @@
         <v>59</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D208" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="44.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D209" s="8"/>
       <c r="F209" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D210" s="8"/>
       <c r="F210" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D211" s="8"/>
       <c r="F211" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K211" s="11"/>
     </row>
@@ -12523,22 +12544,22 @@
         <v>60</v>
       </c>
       <c r="B212" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D212" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K212" s="11"/>
     </row>
@@ -12547,10 +12568,10 @@
       <c r="C213" s="17"/>
       <c r="D213" s="8"/>
       <c r="F213" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K213" s="11"/>
     </row>
@@ -12559,10 +12580,10 @@
       <c r="C214" s="17"/>
       <c r="D214" s="8"/>
       <c r="F214" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K214" s="11"/>
     </row>
@@ -12571,10 +12592,10 @@
       <c r="C215" s="17"/>
       <c r="D215" s="8"/>
       <c r="F215" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K215" s="11"/>
     </row>
@@ -12583,62 +12604,62 @@
         <v>61</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D216" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D217" s="8"/>
       <c r="F217" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="33.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D218" s="8"/>
       <c r="F218" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="44.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D219" s="8"/>
       <c r="F219" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D220" s="8"/>
       <c r="F220" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K220" s="11"/>
     </row>

--- a/documentation/Cases.xlsx
+++ b/documentation/Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="506">
   <si>
     <t xml:space="preserve">Test Case - ID</t>
   </si>
@@ -1056,6 +1056,9 @@
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Кнопка About  не активна и не кликабельна. Переход на страницу About не возможен.</t>
   </si>
   <si>
     <r>
@@ -4717,6 +4720,9 @@
       <c r="G72" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="H72" s="2" t="s">
+        <v>169</v>
+      </c>
       <c r="I72" s="16"/>
       <c r="J72" s="16"/>
     </row>
@@ -4739,10 +4745,10 @@
         <v>32</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>13</v>
@@ -4762,10 +4768,10 @@
         <v>33</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>13</v>
@@ -4795,22 +4801,22 @@
         <v>34</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="39.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4819,10 +4825,10 @@
       <c r="C78" s="17"/>
       <c r="D78" s="8"/>
       <c r="F78" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" s="11" customFormat="true" ht="37.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4830,22 +4836,22 @@
         <v>35</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="3"/>
@@ -4858,10 +4864,10 @@
       <c r="D80" s="8"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="3"/>
@@ -4872,22 +4878,22 @@
         <v>36</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="3"/>
@@ -4900,10 +4906,10 @@
       <c r="D82" s="8"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="3"/>
@@ -4916,10 +4922,10 @@
       <c r="D83" s="8"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="3"/>
@@ -4932,10 +4938,10 @@
       <c r="D84" s="8"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="3"/>
@@ -4948,10 +4954,10 @@
       <c r="D85" s="8"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="3"/>
@@ -4962,22 +4968,22 @@
         <v>37</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="3"/>
@@ -4990,10 +4996,10 @@
       <c r="D87" s="8"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="3"/>
@@ -5006,10 +5012,10 @@
       <c r="D88" s="8"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G88" s="23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="3"/>
@@ -5020,22 +5026,22 @@
         <v>38</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="3"/>
@@ -5048,10 +5054,10 @@
       <c r="D90" s="8"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H90" s="2"/>
       <c r="I90" s="3"/>
@@ -5064,10 +5070,10 @@
       <c r="D91" s="8"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="3"/>
@@ -5080,10 +5086,10 @@
       <c r="D92" s="8"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="3"/>
@@ -5094,22 +5100,22 @@
         <v>39</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="3"/>
@@ -5121,13 +5127,13 @@
       <c r="C94" s="2"/>
       <c r="D94" s="8"/>
       <c r="E94" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="3"/>
@@ -5140,10 +5146,10 @@
       <c r="D95" s="8"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H95" s="2"/>
       <c r="I95" s="3"/>
@@ -5156,10 +5162,10 @@
       <c r="D96" s="8"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H96" s="2"/>
       <c r="I96" s="3"/>
@@ -5170,22 +5176,22 @@
         <v>40</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="3"/>
@@ -5198,10 +5204,10 @@
       <c r="D98" s="8"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="3"/>
@@ -5214,10 +5220,10 @@
       <c r="D99" s="8"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H99" s="2"/>
       <c r="I99" s="3"/>
@@ -5230,10 +5236,10 @@
       <c r="D100" s="8"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="3"/>
@@ -5246,10 +5252,10 @@
       <c r="D101" s="8"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="3"/>
@@ -5260,22 +5266,22 @@
         <v>41</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H102" s="2"/>
       <c r="I102" s="1"/>
@@ -5288,10 +5294,10 @@
       <c r="D103" s="8"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="1"/>
@@ -5304,10 +5310,10 @@
       <c r="D104" s="8"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="1"/>
@@ -5315,7 +5321,7 @@
     </row>
     <row r="105" s="11" customFormat="true" ht="14.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -5332,22 +5338,22 @@
         <v>42</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H106" s="2"/>
       <c r="I106" s="3"/>
@@ -5358,22 +5364,22 @@
         <v>43</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="3"/>
@@ -5386,10 +5392,10 @@
       <c r="D108" s="8"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H108" s="2"/>
       <c r="I108" s="3"/>
@@ -5400,22 +5406,22 @@
         <v>44</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H109" s="2"/>
       <c r="I109" s="3"/>
@@ -5428,10 +5434,10 @@
       <c r="D110" s="8"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H110" s="2"/>
       <c r="I110" s="3"/>
@@ -5442,22 +5448,22 @@
         <v>45</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="3"/>
@@ -5470,10 +5476,10 @@
       <c r="D112" s="8"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="3"/>
@@ -5486,10 +5492,10 @@
       <c r="D113" s="8"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H113" s="2"/>
       <c r="I113" s="3"/>
@@ -5502,10 +5508,10 @@
       <c r="D114" s="8"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H114" s="2"/>
       <c r="I114" s="3"/>
@@ -5518,10 +5524,10 @@
       <c r="D115" s="8"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H115" s="2"/>
       <c r="I115" s="3"/>
@@ -5534,10 +5540,10 @@
       <c r="D116" s="8"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="3"/>
@@ -5548,22 +5554,22 @@
         <v>46</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="3"/>
@@ -5576,10 +5582,10 @@
       <c r="D118" s="8"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="3"/>
@@ -5590,22 +5596,22 @@
         <v>47</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="3"/>
@@ -5618,10 +5624,10 @@
       <c r="D120" s="8"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="3"/>
@@ -5634,10 +5640,10 @@
       <c r="D121" s="8"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="3"/>
@@ -5648,22 +5654,22 @@
         <v>48</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C122" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="3"/>
@@ -5676,10 +5682,10 @@
       <c r="D123" s="8"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H123" s="2"/>
       <c r="I123" s="3"/>
@@ -5692,10 +5698,10 @@
       <c r="D124" s="8"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H124" s="2"/>
       <c r="I124" s="3"/>
@@ -5706,22 +5712,22 @@
         <v>49</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H125" s="2"/>
       <c r="I125" s="3"/>
@@ -5733,13 +5739,13 @@
       <c r="C126" s="2"/>
       <c r="D126" s="8"/>
       <c r="E126" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H126" s="2"/>
       <c r="I126" s="3"/>
@@ -5751,13 +5757,13 @@
       <c r="C127" s="2"/>
       <c r="D127" s="8"/>
       <c r="E127" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H127" s="2"/>
       <c r="I127" s="3"/>
@@ -5770,10 +5776,10 @@
       <c r="D128" s="8"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H128" s="2"/>
       <c r="I128" s="3"/>
@@ -5786,10 +5792,10 @@
       <c r="D129" s="8"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="3"/>
@@ -5802,10 +5808,10 @@
       <c r="D130" s="8"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H130" s="2"/>
       <c r="I130" s="3"/>
@@ -5816,22 +5822,22 @@
         <v>50</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="3"/>
@@ -5844,10 +5850,10 @@
       <c r="D132" s="8"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H132" s="2"/>
       <c r="I132" s="3"/>
@@ -5860,10 +5866,10 @@
       <c r="D133" s="8"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H133" s="2"/>
       <c r="I133" s="3"/>
@@ -5876,10 +5882,10 @@
       <c r="D134" s="8"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H134" s="2"/>
       <c r="I134" s="3"/>
@@ -5892,10 +5898,10 @@
       <c r="D135" s="8"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H135" s="2"/>
       <c r="I135" s="3"/>
@@ -5908,10 +5914,10 @@
       <c r="D136" s="8"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="3"/>
@@ -5922,22 +5928,22 @@
         <v>51</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H137" s="2"/>
       <c r="I137" s="3"/>
@@ -5950,10 +5956,10 @@
       <c r="D138" s="8"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="3"/>
@@ -5966,10 +5972,10 @@
       <c r="D139" s="8"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H139" s="2"/>
       <c r="I139" s="3"/>
@@ -5982,10 +5988,10 @@
       <c r="D140" s="8"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H140" s="2"/>
       <c r="I140" s="3"/>
@@ -5998,10 +6004,10 @@
       <c r="D141" s="8"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H141" s="2"/>
       <c r="I141" s="3"/>
@@ -6014,10 +6020,10 @@
       <c r="D142" s="8"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="3"/>
@@ -6028,22 +6034,22 @@
         <v>52</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="3"/>
@@ -6056,10 +6062,10 @@
       <c r="D144" s="8"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="3"/>
@@ -6072,10 +6078,10 @@
       <c r="D145" s="8"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="3"/>
@@ -6088,10 +6094,10 @@
       <c r="D146" s="8"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="3"/>
@@ -6104,10 +6110,10 @@
       <c r="D147" s="8"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="3"/>
@@ -6120,10 +6126,10 @@
       <c r="D148" s="8"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" s="3"/>
@@ -6131,7 +6137,7 @@
     </row>
     <row r="149" s="11" customFormat="true" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -6148,28 +6154,28 @@
         <v>53</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I150" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J150" s="3"/>
     </row>
@@ -6180,10 +6186,10 @@
       <c r="D151" s="8"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H151" s="2"/>
       <c r="I151" s="16"/>
@@ -6196,10 +6202,10 @@
       <c r="D152" s="8"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H152" s="2"/>
       <c r="I152" s="16"/>
@@ -6212,10 +6218,10 @@
       <c r="D153" s="8"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H153" s="2"/>
       <c r="I153" s="16"/>
@@ -6228,10 +6234,10 @@
       <c r="D154" s="8"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H154" s="2"/>
       <c r="I154" s="16"/>
@@ -6244,10 +6250,10 @@
       <c r="D155" s="8"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="16"/>
@@ -6258,22 +6264,22 @@
         <v>54</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C156" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="3"/>
@@ -6284,22 +6290,22 @@
         <v>55</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H157" s="2"/>
       <c r="I157" s="3"/>
@@ -6312,10 +6318,10 @@
       <c r="D158" s="8"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H158" s="2"/>
       <c r="I158" s="3"/>
@@ -6328,10 +6334,10 @@
       <c r="D159" s="8"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H159" s="2"/>
       <c r="I159" s="3"/>
@@ -6344,10 +6350,10 @@
       <c r="D160" s="8"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H160" s="2"/>
       <c r="I160" s="3"/>
@@ -6360,10 +6366,10 @@
       <c r="D161" s="8"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H161" s="2"/>
       <c r="I161" s="3"/>
@@ -6374,22 +6380,22 @@
         <v>56</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H162" s="2"/>
       <c r="I162" s="3"/>
@@ -6402,10 +6408,10 @@
       <c r="D163" s="8"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H163" s="2"/>
       <c r="I163" s="3"/>
@@ -6418,10 +6424,10 @@
       <c r="D164" s="8"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H164" s="2"/>
       <c r="I164" s="3"/>
@@ -6434,10 +6440,10 @@
       <c r="D165" s="8"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H165" s="2"/>
       <c r="I165" s="3"/>
@@ -6450,10 +6456,10 @@
       <c r="D166" s="8"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H166" s="2"/>
       <c r="I166" s="3"/>
@@ -6466,10 +6472,10 @@
       <c r="D167" s="8"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H167" s="2"/>
       <c r="I167" s="3"/>
@@ -6480,22 +6486,22 @@
         <v>57</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="3"/>
@@ -6508,10 +6514,10 @@
       <c r="D169" s="8"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="3"/>
@@ -6524,10 +6530,10 @@
       <c r="D170" s="8"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H170" s="2"/>
       <c r="I170" s="3"/>
@@ -6540,10 +6546,10 @@
       <c r="D171" s="8"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H171" s="2"/>
       <c r="I171" s="3"/>
@@ -6556,10 +6562,10 @@
       <c r="D172" s="8"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H172" s="2"/>
       <c r="I172" s="3"/>
@@ -6570,22 +6576,22 @@
         <v>58</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H173" s="2"/>
       <c r="I173" s="3"/>
@@ -6598,10 +6604,10 @@
       <c r="D174" s="8"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H174" s="2"/>
       <c r="I174" s="3"/>
@@ -6614,10 +6620,10 @@
       <c r="D175" s="8"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H175" s="2"/>
       <c r="I175" s="3"/>
@@ -6630,10 +6636,10 @@
       <c r="D176" s="8"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H176" s="2"/>
       <c r="I176" s="3"/>
@@ -6646,10 +6652,10 @@
       <c r="D177" s="8"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H177" s="2"/>
       <c r="I177" s="3"/>
@@ -6660,22 +6666,22 @@
         <v>59</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H178" s="2"/>
       <c r="I178" s="3"/>
@@ -6688,10 +6694,10 @@
       <c r="D179" s="8"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H179" s="2"/>
       <c r="I179" s="3"/>
@@ -6704,10 +6710,10 @@
       <c r="D180" s="8"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H180" s="2"/>
       <c r="I180" s="3"/>
@@ -6720,10 +6726,10 @@
       <c r="D181" s="8"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H181" s="2"/>
       <c r="I181" s="3"/>
@@ -6736,10 +6742,10 @@
       <c r="D182" s="8"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H182" s="2"/>
       <c r="I182" s="3"/>
@@ -6750,22 +6756,22 @@
         <v>60</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H183" s="2"/>
       <c r="I183" s="3"/>
@@ -6778,10 +6784,10 @@
       <c r="D184" s="8"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H184" s="2"/>
       <c r="I184" s="3"/>
@@ -6794,10 +6800,10 @@
       <c r="D185" s="8"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H185" s="2"/>
       <c r="I185" s="3"/>
@@ -6810,10 +6816,10 @@
       <c r="D186" s="8"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H186" s="2"/>
       <c r="I186" s="3"/>
@@ -6826,10 +6832,10 @@
       <c r="D187" s="8"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H187" s="2"/>
       <c r="I187" s="3"/>
@@ -6840,22 +6846,22 @@
         <v>61</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H188" s="2"/>
       <c r="I188" s="3"/>
@@ -6868,10 +6874,10 @@
       <c r="D189" s="8"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H189" s="2"/>
       <c r="I189" s="3"/>
@@ -6879,7 +6885,7 @@
     </row>
     <row r="190" s="11" customFormat="true" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B190" s="20"/>
       <c r="C190" s="20"/>
@@ -6896,22 +6902,22 @@
         <v>62</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D191" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H191" s="2"/>
       <c r="I191" s="3"/>
@@ -6924,10 +6930,10 @@
       <c r="D192" s="8"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H192" s="2"/>
       <c r="I192" s="3"/>
@@ -6940,10 +6946,10 @@
       <c r="D193" s="8"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H193" s="2"/>
       <c r="I193" s="3"/>
@@ -6956,10 +6962,10 @@
       <c r="D194" s="8"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H194" s="2"/>
       <c r="I194" s="3"/>
@@ -6970,22 +6976,22 @@
         <v>63</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H195" s="2"/>
       <c r="I195" s="3"/>
@@ -6998,10 +7004,10 @@
       <c r="D196" s="8"/>
       <c r="E196" s="23"/>
       <c r="F196" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H196" s="2"/>
       <c r="I196" s="3"/>
@@ -7014,10 +7020,10 @@
       <c r="D197" s="8"/>
       <c r="E197" s="23"/>
       <c r="F197" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H197" s="2"/>
       <c r="I197" s="3"/>
@@ -7030,10 +7036,10 @@
       <c r="D198" s="8"/>
       <c r="E198" s="23"/>
       <c r="F198" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H198" s="2"/>
       <c r="I198" s="3"/>
@@ -7044,22 +7050,22 @@
         <v>64</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D199" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H199" s="2"/>
       <c r="I199" s="3"/>
@@ -7072,10 +7078,10 @@
       <c r="D200" s="8"/>
       <c r="E200" s="23"/>
       <c r="F200" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H200" s="2"/>
       <c r="I200" s="3"/>
@@ -7088,10 +7094,10 @@
       <c r="D201" s="8"/>
       <c r="E201" s="23"/>
       <c r="F201" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H201" s="2"/>
       <c r="I201" s="3"/>
@@ -7104,10 +7110,10 @@
       <c r="D202" s="8"/>
       <c r="E202" s="23"/>
       <c r="F202" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H202" s="2"/>
       <c r="I202" s="3"/>
@@ -7118,22 +7124,22 @@
         <v>65</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D203" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H203" s="2"/>
       <c r="I203" s="3"/>
@@ -7146,10 +7152,10 @@
       <c r="D204" s="8"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H204" s="2"/>
       <c r="I204" s="3"/>
@@ -7162,10 +7168,10 @@
       <c r="D205" s="8"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H205" s="2"/>
       <c r="I205" s="3"/>
@@ -7178,10 +7184,10 @@
       <c r="D206" s="8"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H206" s="2"/>
       <c r="I206" s="3"/>
@@ -7192,22 +7198,22 @@
         <v>66</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C207" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D207" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H207" s="2"/>
       <c r="I207" s="3"/>
@@ -7220,10 +7226,10 @@
       <c r="D208" s="8"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H208" s="2"/>
       <c r="I208" s="3"/>
@@ -7236,10 +7242,10 @@
       <c r="D209" s="8"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H209" s="2"/>
       <c r="I209" s="3"/>
@@ -7252,10 +7258,10 @@
       <c r="D210" s="8"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H210" s="2"/>
       <c r="I210" s="3"/>
@@ -7266,22 +7272,22 @@
         <v>67</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C211" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D211" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H211" s="2"/>
       <c r="I211" s="3"/>
@@ -7294,10 +7300,10 @@
       <c r="D212" s="8"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H212" s="2"/>
       <c r="I212" s="3"/>
@@ -7310,10 +7316,10 @@
       <c r="D213" s="8"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H213" s="2"/>
       <c r="I213" s="3"/>
@@ -7324,22 +7330,22 @@
         <v>68</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D214" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H214" s="2"/>
       <c r="I214" s="3"/>
@@ -7352,10 +7358,10 @@
       <c r="D215" s="8"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H215" s="2"/>
       <c r="I215" s="3"/>
@@ -7368,10 +7374,10 @@
       <c r="D216" s="8"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H216" s="2"/>
       <c r="I216" s="3"/>
@@ -7384,10 +7390,10 @@
       <c r="D217" s="8"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H217" s="2"/>
       <c r="I217" s="3"/>
@@ -7398,22 +7404,22 @@
         <v>69</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D218" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H218" s="2"/>
       <c r="I218" s="3"/>
@@ -7426,10 +7432,10 @@
       <c r="D219" s="8"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H219" s="2"/>
       <c r="I219" s="3"/>
@@ -7442,10 +7448,10 @@
       <c r="D220" s="8"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H220" s="2"/>
       <c r="I220" s="3"/>
@@ -7458,10 +7464,10 @@
       <c r="D221" s="8"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H221" s="2"/>
       <c r="I221" s="3"/>
@@ -7472,22 +7478,22 @@
         <v>70</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H222" s="2"/>
       <c r="I222" s="3"/>
@@ -7500,10 +7506,10 @@
       <c r="D223" s="8"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H223" s="2"/>
       <c r="I223" s="3"/>
@@ -7516,10 +7522,10 @@
       <c r="D224" s="8"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H224" s="2"/>
       <c r="I224" s="3"/>
@@ -7532,10 +7538,10 @@
       <c r="D225" s="8"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H225" s="2"/>
       <c r="I225" s="3"/>
@@ -7546,22 +7552,22 @@
         <v>71</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H226" s="2"/>
       <c r="I226" s="3"/>
@@ -7574,10 +7580,10 @@
       <c r="D227" s="8"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H227" s="2"/>
       <c r="I227" s="3"/>
@@ -7590,10 +7596,10 @@
       <c r="D228" s="8"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H228" s="2"/>
       <c r="I228" s="3"/>
@@ -7606,10 +7612,10 @@
       <c r="D229" s="8"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H229" s="2"/>
       <c r="I229" s="3"/>
@@ -7620,22 +7626,22 @@
         <v>72</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H230" s="2"/>
       <c r="I230" s="3"/>
@@ -7648,10 +7654,10 @@
       <c r="D231" s="8"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H231" s="2"/>
       <c r="I231" s="3"/>
@@ -7664,10 +7670,10 @@
       <c r="D232" s="8"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H232" s="2"/>
       <c r="I232" s="3"/>
@@ -7680,10 +7686,10 @@
       <c r="D233" s="8"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H233" s="2"/>
       <c r="I233" s="3"/>
@@ -7696,10 +7702,10 @@
       <c r="D234" s="8"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H234" s="2"/>
       <c r="I234" s="3"/>
@@ -7710,22 +7716,22 @@
         <v>73</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D235" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H235" s="2"/>
       <c r="I235" s="1"/>
@@ -7738,10 +7744,10 @@
       <c r="D236" s="8"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H236" s="2"/>
       <c r="I236" s="1"/>
@@ -7749,7 +7755,7 @@
     </row>
     <row r="237" s="11" customFormat="true" ht="14.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -7766,22 +7772,22 @@
         <v>74</v>
       </c>
       <c r="B238" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C238" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D238" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H238" s="2"/>
       <c r="I238" s="3"/>
@@ -7792,19 +7798,19 @@
         <v>75</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C239" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D239" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>27</v>
@@ -7818,22 +7824,22 @@
         <v>76</v>
       </c>
       <c r="B240" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C240" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D240" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H240" s="2"/>
       <c r="I240" s="1"/>
@@ -7846,10 +7852,10 @@
       <c r="D241" s="8"/>
       <c r="E241" s="2"/>
       <c r="F241" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H241" s="2"/>
       <c r="I241" s="1"/>
@@ -7860,22 +7866,22 @@
         <v>77</v>
       </c>
       <c r="B242" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C242" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D242" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H242" s="2"/>
       <c r="I242" s="3"/>
@@ -7888,10 +7894,10 @@
       <c r="D243" s="8"/>
       <c r="E243" s="2"/>
       <c r="F243" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H243" s="2"/>
       <c r="I243" s="3"/>
@@ -7904,10 +7910,10 @@
       <c r="D244" s="8"/>
       <c r="E244" s="2"/>
       <c r="F244" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H244" s="2"/>
       <c r="I244" s="3"/>
@@ -7918,22 +7924,22 @@
         <v>78</v>
       </c>
       <c r="B245" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C245" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D245" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H245" s="2"/>
       <c r="I245" s="3"/>
@@ -7946,10 +7952,10 @@
       <c r="D246" s="8"/>
       <c r="E246" s="2"/>
       <c r="F246" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H246" s="2"/>
       <c r="I246" s="3"/>
@@ -7962,10 +7968,10 @@
       <c r="D247" s="8"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H247" s="2"/>
       <c r="I247" s="3"/>
@@ -7978,10 +7984,10 @@
       <c r="D248" s="8"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H248" s="2"/>
       <c r="I248" s="3"/>
@@ -7992,28 +7998,28 @@
         <v>79</v>
       </c>
       <c r="B249" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C249" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D249" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I249" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J249" s="3"/>
     </row>
@@ -8024,10 +8030,10 @@
       <c r="D250" s="8"/>
       <c r="E250" s="2"/>
       <c r="F250" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H250" s="2"/>
       <c r="I250" s="16"/>
@@ -8040,10 +8046,10 @@
       <c r="D251" s="8"/>
       <c r="E251" s="2"/>
       <c r="F251" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H251" s="2"/>
       <c r="I251" s="16"/>
@@ -8056,10 +8062,10 @@
       <c r="D252" s="8"/>
       <c r="E252" s="2"/>
       <c r="F252" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H252" s="2"/>
       <c r="I252" s="16"/>
@@ -8070,22 +8076,22 @@
         <v>80</v>
       </c>
       <c r="B253" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C253" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H253" s="2"/>
       <c r="I253" s="3"/>
@@ -8098,10 +8104,10 @@
       <c r="D254" s="8"/>
       <c r="E254" s="2"/>
       <c r="F254" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H254" s="2"/>
       <c r="I254" s="3"/>
@@ -8112,22 +8118,22 @@
         <v>81</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C255" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D255" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H255" s="2"/>
       <c r="I255" s="3"/>
@@ -8140,10 +8146,10 @@
       <c r="D256" s="8"/>
       <c r="E256" s="2"/>
       <c r="F256" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H256" s="2"/>
       <c r="I256" s="3"/>
@@ -8154,22 +8160,22 @@
         <v>82</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C257" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D257" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H257" s="2"/>
       <c r="I257" s="3"/>
@@ -8182,10 +8188,10 @@
       <c r="D258" s="8"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H258" s="2"/>
       <c r="I258" s="3"/>
@@ -8196,22 +8202,22 @@
         <v>83</v>
       </c>
       <c r="B259" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C259" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D259" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H259" s="2"/>
       <c r="I259" s="3"/>
@@ -8224,10 +8230,10 @@
       <c r="D260" s="8"/>
       <c r="E260" s="2"/>
       <c r="F260" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H260" s="2"/>
       <c r="I260" s="3"/>
@@ -8240,10 +8246,10 @@
       <c r="D261" s="8"/>
       <c r="E261" s="2"/>
       <c r="F261" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H261" s="2"/>
       <c r="I261" s="3"/>
@@ -8254,22 +8260,22 @@
         <v>84</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C262" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D262" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H262" s="2"/>
       <c r="I262" s="3"/>
@@ -8282,10 +8288,10 @@
       <c r="D263" s="8"/>
       <c r="E263" s="2"/>
       <c r="F263" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H263" s="2"/>
       <c r="I263" s="3"/>
@@ -8298,10 +8304,10 @@
       <c r="D264" s="8"/>
       <c r="E264" s="2"/>
       <c r="F264" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H264" s="2"/>
       <c r="I264" s="3"/>
@@ -8314,10 +8320,10 @@
       <c r="D265" s="8"/>
       <c r="E265" s="2"/>
       <c r="F265" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H265" s="2"/>
       <c r="I265" s="3"/>
@@ -8330,10 +8336,10 @@
       <c r="D266" s="8"/>
       <c r="E266" s="2"/>
       <c r="F266" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H266" s="2"/>
       <c r="I266" s="3"/>
@@ -8344,22 +8350,22 @@
         <v>85</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C267" s="17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D267" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H267" s="2"/>
       <c r="I267" s="3"/>
@@ -8372,10 +8378,10 @@
       <c r="D268" s="8"/>
       <c r="E268" s="2"/>
       <c r="F268" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H268" s="2"/>
       <c r="I268" s="3"/>
@@ -8388,10 +8394,10 @@
       <c r="D269" s="8"/>
       <c r="E269" s="2"/>
       <c r="F269" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H269" s="2"/>
       <c r="I269" s="3"/>
@@ -8402,22 +8408,22 @@
         <v>86</v>
       </c>
       <c r="B270" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C270" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D270" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H270" s="2"/>
       <c r="I270" s="3"/>
@@ -8430,10 +8436,10 @@
       <c r="D271" s="8"/>
       <c r="E271" s="2"/>
       <c r="F271" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H271" s="2"/>
       <c r="I271" s="3"/>
@@ -8446,10 +8452,10 @@
       <c r="D272" s="8"/>
       <c r="E272" s="2"/>
       <c r="F272" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H272" s="2"/>
       <c r="I272" s="3"/>
@@ -8460,22 +8466,22 @@
         <v>87</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C273" s="17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D273" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H273" s="2"/>
       <c r="I273" s="3"/>
@@ -8488,10 +8494,10 @@
       <c r="D274" s="8"/>
       <c r="E274" s="2"/>
       <c r="F274" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H274" s="2"/>
       <c r="I274" s="3"/>
@@ -8504,10 +8510,10 @@
       <c r="D275" s="8"/>
       <c r="E275" s="2"/>
       <c r="F275" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H275" s="2"/>
       <c r="I275" s="3"/>
@@ -8518,25 +8524,25 @@
         <v>88</v>
       </c>
       <c r="B276" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C276" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D276" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
@@ -8548,10 +8554,10 @@
       <c r="D277" s="8"/>
       <c r="E277" s="2"/>
       <c r="F277" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H277" s="2"/>
       <c r="I277" s="3"/>
@@ -8564,10 +8570,10 @@
       <c r="D278" s="8"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H278" s="2"/>
       <c r="I278" s="3"/>
@@ -8578,22 +8584,22 @@
         <v>89</v>
       </c>
       <c r="B279" s="17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C279" s="17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D279" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H279" s="2"/>
       <c r="I279" s="3"/>
@@ -8606,10 +8612,10 @@
       <c r="D280" s="8"/>
       <c r="E280" s="2"/>
       <c r="F280" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H280" s="2"/>
       <c r="I280" s="3"/>
@@ -8622,10 +8628,10 @@
       <c r="D281" s="8"/>
       <c r="E281" s="2"/>
       <c r="F281" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H281" s="2"/>
       <c r="I281" s="3"/>
@@ -9818,7 +9824,7 @@
         <v>84</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9899,7 +9905,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -9916,10 +9922,10 @@
         <v>13</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>13</v>
@@ -9934,10 +9940,10 @@
         <v>95</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9958,10 +9964,10 @@
       <c r="C39" s="17"/>
       <c r="D39" s="8"/>
       <c r="F39" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I39" s="16"/>
       <c r="J39" s="16"/>
@@ -9971,10 +9977,10 @@
       <c r="C40" s="17"/>
       <c r="D40" s="8"/>
       <c r="F40" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="16"/>
@@ -9984,10 +9990,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>13</v>
@@ -10022,10 +10028,10 @@
       <c r="C43" s="17"/>
       <c r="D43" s="8"/>
       <c r="F43" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
@@ -10035,10 +10041,10 @@
       <c r="C44" s="17"/>
       <c r="D44" s="8"/>
       <c r="F44" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I44" s="16"/>
       <c r="J44" s="16"/>
@@ -10048,10 +10054,10 @@
       <c r="C45" s="17"/>
       <c r="D45" s="8"/>
       <c r="F45" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I45" s="16"/>
       <c r="J45" s="16"/>
@@ -10061,10 +10067,10 @@
       <c r="C46" s="17"/>
       <c r="D46" s="8"/>
       <c r="F46" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="16"/>
@@ -10143,7 +10149,7 @@
         <v>17</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>116</v>
@@ -10226,7 +10232,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>13</v>
@@ -10367,22 +10373,22 @@
         <v>23</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K63" s="11"/>
     </row>
@@ -10391,10 +10397,10 @@
       <c r="C64" s="17"/>
       <c r="D64" s="8"/>
       <c r="F64" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K64" s="11"/>
     </row>
@@ -10403,22 +10409,22 @@
         <v>24</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K65" s="11"/>
     </row>
@@ -10427,10 +10433,10 @@
       <c r="C66" s="17"/>
       <c r="D66" s="8"/>
       <c r="F66" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K66" s="11"/>
     </row>
@@ -10439,22 +10445,22 @@
         <v>25</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K67" s="11"/>
     </row>
@@ -10462,10 +10468,10 @@
       <c r="A68" s="25"/>
       <c r="D68" s="8"/>
       <c r="F68" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K68" s="11"/>
     </row>
@@ -10473,10 +10479,10 @@
       <c r="A69" s="25"/>
       <c r="D69" s="8"/>
       <c r="F69" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K69" s="11"/>
     </row>
@@ -10484,10 +10490,10 @@
       <c r="A70" s="25"/>
       <c r="D70" s="8"/>
       <c r="F70" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K70" s="11"/>
     </row>
@@ -10495,10 +10501,10 @@
       <c r="A71" s="25"/>
       <c r="D71" s="8"/>
       <c r="F71" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K71" s="11"/>
     </row>
@@ -10507,22 +10513,22 @@
         <v>26</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K72" s="11"/>
     </row>
@@ -10530,10 +10536,10 @@
       <c r="A73" s="25"/>
       <c r="D73" s="8"/>
       <c r="F73" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K73" s="11"/>
     </row>
@@ -10541,10 +10547,10 @@
       <c r="A74" s="25"/>
       <c r="D74" s="8"/>
       <c r="F74" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G74" s="23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K74" s="11"/>
     </row>
@@ -10553,22 +10559,22 @@
         <v>27</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K75" s="11"/>
     </row>
@@ -10577,10 +10583,10 @@
       <c r="C76" s="17"/>
       <c r="D76" s="8"/>
       <c r="F76" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K76" s="11"/>
     </row>
@@ -10589,10 +10595,10 @@
       <c r="C77" s="17"/>
       <c r="D77" s="8"/>
       <c r="F77" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K77" s="11"/>
     </row>
@@ -10601,10 +10607,10 @@
       <c r="C78" s="17"/>
       <c r="D78" s="8"/>
       <c r="F78" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K78" s="11"/>
     </row>
@@ -10613,55 +10619,55 @@
         <v>28</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K79" s="11"/>
     </row>
     <row r="80" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D80" s="8"/>
       <c r="E80" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K80" s="11"/>
     </row>
     <row r="81" customFormat="false" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D81" s="8"/>
       <c r="F81" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K81" s="11"/>
     </row>
     <row r="82" customFormat="false" ht="33.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D82" s="8"/>
       <c r="F82" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K82" s="11"/>
     </row>
@@ -10670,62 +10676,62 @@
         <v>29</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K83" s="11"/>
     </row>
     <row r="84" customFormat="false" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D84" s="8"/>
       <c r="F84" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K84" s="11"/>
     </row>
     <row r="85" customFormat="false" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="8"/>
       <c r="F85" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K85" s="11"/>
     </row>
     <row r="86" customFormat="false" ht="32.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D86" s="8"/>
       <c r="F86" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K86" s="11"/>
     </row>
     <row r="87" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D87" s="8"/>
       <c r="F87" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K87" s="11"/>
     </row>
@@ -10734,22 +10740,22 @@
         <v>30</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I88" s="1"/>
       <c r="K88" s="11"/>
@@ -10759,10 +10765,10 @@
       <c r="C89" s="17"/>
       <c r="D89" s="8"/>
       <c r="F89" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -10773,10 +10779,10 @@
       <c r="C90" s="17"/>
       <c r="D90" s="8"/>
       <c r="F90" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -10784,7 +10790,7 @@
     </row>
     <row r="91" customFormat="false" ht="14.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -10802,22 +10808,22 @@
         <v>31</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K92" s="11"/>
     </row>
@@ -10826,22 +10832,22 @@
         <v>32</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K93" s="11"/>
     </row>
@@ -10850,10 +10856,10 @@
       <c r="C94" s="17"/>
       <c r="D94" s="8"/>
       <c r="F94" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K94" s="11"/>
     </row>
@@ -10862,22 +10868,22 @@
         <v>33</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K95" s="11"/>
     </row>
@@ -10886,10 +10892,10 @@
       <c r="C96" s="17"/>
       <c r="D96" s="8"/>
       <c r="F96" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K96" s="11"/>
     </row>
@@ -10898,22 +10904,22 @@
         <v>34</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K97" s="11"/>
     </row>
@@ -10922,10 +10928,10 @@
       <c r="C98" s="17"/>
       <c r="D98" s="8"/>
       <c r="F98" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K98" s="11"/>
     </row>
@@ -10934,10 +10940,10 @@
       <c r="C99" s="17"/>
       <c r="D99" s="8"/>
       <c r="F99" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K99" s="11"/>
     </row>
@@ -10946,10 +10952,10 @@
       <c r="C100" s="17"/>
       <c r="D100" s="8"/>
       <c r="F100" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K100" s="11"/>
     </row>
@@ -10958,10 +10964,10 @@
       <c r="C101" s="17"/>
       <c r="D101" s="8"/>
       <c r="F101" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K101" s="11"/>
     </row>
@@ -10970,10 +10976,10 @@
       <c r="C102" s="17"/>
       <c r="D102" s="8"/>
       <c r="F102" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K102" s="11"/>
     </row>
@@ -10982,32 +10988,32 @@
         <v>35</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K103" s="11"/>
     </row>
     <row r="104" customFormat="false" ht="97.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D104" s="8"/>
       <c r="F104" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K104" s="11"/>
     </row>
@@ -11016,22 +11022,22 @@
         <v>36</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K105" s="11"/>
     </row>
@@ -11040,10 +11046,10 @@
       <c r="C106" s="17"/>
       <c r="D106" s="8"/>
       <c r="F106" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K106" s="11"/>
     </row>
@@ -11052,10 +11058,10 @@
       <c r="C107" s="17"/>
       <c r="D107" s="8"/>
       <c r="F107" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K107" s="11"/>
     </row>
@@ -11064,22 +11070,22 @@
         <v>37</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K108" s="11"/>
     </row>
@@ -11088,10 +11094,10 @@
       <c r="C109" s="17"/>
       <c r="D109" s="8"/>
       <c r="F109" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K109" s="11"/>
     </row>
@@ -11100,10 +11106,10 @@
       <c r="C110" s="17"/>
       <c r="D110" s="8"/>
       <c r="F110" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K110" s="11"/>
     </row>
@@ -11112,78 +11118,78 @@
         <v>38</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K111" s="11"/>
     </row>
     <row r="112" customFormat="false" ht="24.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D112" s="8"/>
       <c r="E112" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K112" s="11"/>
     </row>
     <row r="113" customFormat="false" ht="23.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D113" s="8"/>
       <c r="E113" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K113" s="11"/>
     </row>
     <row r="114" customFormat="false" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D114" s="8"/>
       <c r="F114" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K114" s="11"/>
     </row>
     <row r="115" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D115" s="8"/>
       <c r="F115" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K115" s="11"/>
     </row>
     <row r="116" customFormat="false" ht="39.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D116" s="8"/>
       <c r="F116" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K116" s="11"/>
     </row>
@@ -11192,22 +11198,22 @@
         <v>39</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K117" s="11"/>
     </row>
@@ -11216,10 +11222,10 @@
       <c r="C118" s="17"/>
       <c r="D118" s="8"/>
       <c r="F118" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K118" s="11"/>
     </row>
@@ -11228,10 +11234,10 @@
       <c r="C119" s="17"/>
       <c r="D119" s="8"/>
       <c r="F119" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K119" s="11"/>
     </row>
@@ -11240,10 +11246,10 @@
       <c r="C120" s="17"/>
       <c r="D120" s="8"/>
       <c r="F120" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K120" s="11"/>
     </row>
@@ -11252,10 +11258,10 @@
       <c r="C121" s="17"/>
       <c r="D121" s="8"/>
       <c r="F121" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K121" s="11"/>
     </row>
@@ -11264,10 +11270,10 @@
       <c r="C122" s="17"/>
       <c r="D122" s="8"/>
       <c r="F122" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K122" s="11"/>
     </row>
@@ -11276,22 +11282,22 @@
         <v>40</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K123" s="11"/>
     </row>
@@ -11300,10 +11306,10 @@
       <c r="C124" s="17"/>
       <c r="D124" s="8"/>
       <c r="F124" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K124" s="11"/>
     </row>
@@ -11312,10 +11318,10 @@
       <c r="C125" s="17"/>
       <c r="D125" s="8"/>
       <c r="F125" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K125" s="11"/>
     </row>
@@ -11324,10 +11330,10 @@
       <c r="C126" s="17"/>
       <c r="D126" s="8"/>
       <c r="F126" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K126" s="11"/>
     </row>
@@ -11336,10 +11342,10 @@
       <c r="C127" s="17"/>
       <c r="D127" s="8"/>
       <c r="F127" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K127" s="11"/>
     </row>
@@ -11348,10 +11354,10 @@
       <c r="C128" s="17"/>
       <c r="D128" s="8"/>
       <c r="F128" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K128" s="11"/>
     </row>
@@ -11360,78 +11366,78 @@
         <v>41</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K129" s="11"/>
     </row>
     <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D130" s="8"/>
       <c r="F130" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K130" s="11"/>
     </row>
     <row r="131" customFormat="false" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D131" s="8"/>
       <c r="F131" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K131" s="11"/>
     </row>
     <row r="132" customFormat="false" ht="22.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D132" s="8"/>
       <c r="F132" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K132" s="11"/>
     </row>
     <row r="133" customFormat="false" ht="26.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D133" s="8"/>
       <c r="F133" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K133" s="11"/>
     </row>
     <row r="134" customFormat="false" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D134" s="8"/>
       <c r="F134" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K134" s="11"/>
     </row>
     <row r="135" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -11449,28 +11455,28 @@
         <v>42</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D136" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I136" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K136" s="11"/>
     </row>
@@ -11479,10 +11485,10 @@
       <c r="C137" s="17"/>
       <c r="D137" s="8"/>
       <c r="F137" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I137" s="16"/>
       <c r="K137" s="11"/>
@@ -11492,10 +11498,10 @@
       <c r="C138" s="17"/>
       <c r="D138" s="8"/>
       <c r="F138" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I138" s="16"/>
       <c r="K138" s="11"/>
@@ -11505,10 +11511,10 @@
       <c r="C139" s="17"/>
       <c r="D139" s="8"/>
       <c r="F139" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I139" s="16"/>
       <c r="K139" s="11"/>
@@ -11518,10 +11524,10 @@
       <c r="C140" s="17"/>
       <c r="D140" s="8"/>
       <c r="F140" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I140" s="16"/>
       <c r="K140" s="11"/>
@@ -11531,10 +11537,10 @@
       <c r="C141" s="17"/>
       <c r="D141" s="8"/>
       <c r="F141" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I141" s="16"/>
       <c r="K141" s="11"/>
@@ -11544,22 +11550,22 @@
         <v>43</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D142" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K142" s="11"/>
     </row>
@@ -11568,22 +11574,22 @@
         <v>44</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K143" s="11"/>
     </row>
@@ -11592,10 +11598,10 @@
       <c r="C144" s="17"/>
       <c r="D144" s="8"/>
       <c r="F144" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K144" s="11"/>
     </row>
@@ -11604,10 +11610,10 @@
       <c r="C145" s="17"/>
       <c r="D145" s="8"/>
       <c r="F145" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K145" s="11"/>
     </row>
@@ -11616,10 +11622,10 @@
       <c r="C146" s="17"/>
       <c r="D146" s="8"/>
       <c r="F146" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K146" s="11"/>
     </row>
@@ -11628,10 +11634,10 @@
       <c r="C147" s="17"/>
       <c r="D147" s="8"/>
       <c r="F147" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K147" s="11"/>
     </row>
@@ -11640,22 +11646,22 @@
         <v>45</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K148" s="11"/>
     </row>
@@ -11664,10 +11670,10 @@
       <c r="C149" s="17"/>
       <c r="D149" s="8"/>
       <c r="F149" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K149" s="11"/>
     </row>
@@ -11676,10 +11682,10 @@
       <c r="C150" s="17"/>
       <c r="D150" s="8"/>
       <c r="F150" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K150" s="11"/>
     </row>
@@ -11688,10 +11694,10 @@
       <c r="C151" s="17"/>
       <c r="D151" s="8"/>
       <c r="F151" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K151" s="11"/>
     </row>
@@ -11700,10 +11706,10 @@
       <c r="C152" s="17"/>
       <c r="D152" s="8"/>
       <c r="F152" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K152" s="11"/>
     </row>
@@ -11712,10 +11718,10 @@
       <c r="C153" s="17"/>
       <c r="D153" s="8"/>
       <c r="F153" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K153" s="11"/>
     </row>
@@ -11724,22 +11730,22 @@
         <v>46</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K154" s="11"/>
     </row>
@@ -11748,10 +11754,10 @@
       <c r="C155" s="17"/>
       <c r="D155" s="8"/>
       <c r="F155" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K155" s="11"/>
     </row>
@@ -11760,10 +11766,10 @@
       <c r="C156" s="17"/>
       <c r="D156" s="8"/>
       <c r="F156" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K156" s="11"/>
     </row>
@@ -11772,10 +11778,10 @@
       <c r="C157" s="17"/>
       <c r="D157" s="8"/>
       <c r="F157" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K157" s="11"/>
     </row>
@@ -11784,10 +11790,10 @@
       <c r="C158" s="17"/>
       <c r="D158" s="8"/>
       <c r="F158" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K158" s="11"/>
     </row>
@@ -11796,62 +11802,62 @@
         <v>47</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K159" s="11"/>
     </row>
     <row r="160" customFormat="false" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D160" s="8"/>
       <c r="F160" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K160" s="11"/>
     </row>
     <row r="161" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D161" s="8"/>
       <c r="F161" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K161" s="11"/>
     </row>
     <row r="162" customFormat="false" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D162" s="8"/>
       <c r="F162" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K162" s="11"/>
     </row>
     <row r="163" customFormat="false" ht="69.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D163" s="8"/>
       <c r="F163" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K163" s="11"/>
     </row>
@@ -11860,62 +11866,62 @@
         <v>48</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K164" s="11"/>
     </row>
     <row r="165" customFormat="false" ht="31.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D165" s="8"/>
       <c r="F165" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K165" s="11"/>
     </row>
     <row r="166" customFormat="false" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D166" s="8"/>
       <c r="F166" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K166" s="11"/>
     </row>
     <row r="167" customFormat="false" ht="30.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D167" s="8"/>
       <c r="F167" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K167" s="11"/>
     </row>
     <row r="168" customFormat="false" ht="62.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D168" s="8"/>
       <c r="F168" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K168" s="11"/>
     </row>
@@ -11924,62 +11930,62 @@
         <v>49</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K169" s="11"/>
     </row>
     <row r="170" customFormat="false" ht="27.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D170" s="8"/>
       <c r="F170" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K170" s="11"/>
     </row>
     <row r="171" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D171" s="8"/>
       <c r="F171" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K171" s="11"/>
     </row>
     <row r="172" customFormat="false" ht="39.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D172" s="8"/>
       <c r="F172" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K172" s="11"/>
     </row>
     <row r="173" customFormat="false" ht="57.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D173" s="8"/>
       <c r="F173" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K173" s="11"/>
     </row>
@@ -11988,22 +11994,22 @@
         <v>50</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D174" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K174" s="11"/>
     </row>
@@ -12011,16 +12017,16 @@
       <c r="B175" s="17"/>
       <c r="D175" s="8"/>
       <c r="F175" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K175" s="11"/>
     </row>
     <row r="176" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B176" s="20"/>
       <c r="C176" s="20"/>
@@ -12038,52 +12044,52 @@
         <v>51</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K177" s="11"/>
     </row>
     <row r="178" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D178" s="8"/>
       <c r="F178" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K178" s="11"/>
     </row>
     <row r="179" customFormat="false" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D179" s="8"/>
       <c r="F179" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K179" s="11"/>
     </row>
     <row r="180" customFormat="false" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D180" s="8"/>
       <c r="F180" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K180" s="11"/>
     </row>
@@ -12092,22 +12098,22 @@
         <v>52</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D181" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K181" s="11"/>
     </row>
@@ -12117,10 +12123,10 @@
       <c r="D182" s="8"/>
       <c r="E182" s="23"/>
       <c r="F182" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K182" s="11"/>
     </row>
@@ -12130,10 +12136,10 @@
       <c r="D183" s="8"/>
       <c r="E183" s="23"/>
       <c r="F183" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K183" s="11"/>
     </row>
@@ -12143,10 +12149,10 @@
       <c r="D184" s="8"/>
       <c r="E184" s="23"/>
       <c r="F184" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K184" s="11"/>
     </row>
@@ -12155,22 +12161,22 @@
         <v>53</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D185" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K185" s="11"/>
     </row>
@@ -12180,10 +12186,10 @@
       <c r="D186" s="8"/>
       <c r="E186" s="23"/>
       <c r="F186" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K186" s="11"/>
     </row>
@@ -12193,10 +12199,10 @@
       <c r="D187" s="8"/>
       <c r="E187" s="23"/>
       <c r="F187" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K187" s="11"/>
     </row>
@@ -12206,10 +12212,10 @@
       <c r="D188" s="8"/>
       <c r="E188" s="23"/>
       <c r="F188" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K188" s="11"/>
     </row>
@@ -12218,22 +12224,22 @@
         <v>54</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D189" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K189" s="11"/>
     </row>
@@ -12242,10 +12248,10 @@
       <c r="C190" s="17"/>
       <c r="D190" s="8"/>
       <c r="F190" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K190" s="11"/>
     </row>
@@ -12254,10 +12260,10 @@
       <c r="C191" s="17"/>
       <c r="D191" s="8"/>
       <c r="F191" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K191" s="11"/>
     </row>
@@ -12266,10 +12272,10 @@
       <c r="C192" s="17"/>
       <c r="D192" s="8"/>
       <c r="F192" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K192" s="11"/>
     </row>
@@ -12278,22 +12284,22 @@
         <v>55</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C193" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K193" s="11"/>
     </row>
@@ -12302,10 +12308,10 @@
       <c r="C194" s="17"/>
       <c r="D194" s="8"/>
       <c r="F194" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K194" s="11"/>
     </row>
@@ -12314,10 +12320,10 @@
       <c r="C195" s="17"/>
       <c r="D195" s="8"/>
       <c r="F195" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K195" s="11"/>
     </row>
@@ -12326,10 +12332,10 @@
       <c r="C196" s="17"/>
       <c r="D196" s="8"/>
       <c r="F196" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K196" s="11"/>
     </row>
@@ -12338,42 +12344,42 @@
         <v>56</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C197" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D198" s="8"/>
       <c r="F198" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="44.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D199" s="8"/>
       <c r="F199" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K199" s="11"/>
     </row>
@@ -12382,52 +12388,52 @@
         <v>57</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D200" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D201" s="8"/>
       <c r="F201" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K201" s="11"/>
     </row>
     <row r="202" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D202" s="8"/>
       <c r="F202" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K202" s="11"/>
     </row>
     <row r="203" customFormat="false" ht="40.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D203" s="8"/>
       <c r="F203" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K203" s="11"/>
     </row>
@@ -12436,52 +12442,52 @@
         <v>58</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D204" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="31.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D205" s="8"/>
       <c r="F205" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K205" s="11"/>
     </row>
     <row r="206" customFormat="false" ht="29.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D206" s="8"/>
       <c r="F206" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K206" s="11"/>
     </row>
     <row r="207" customFormat="false" ht="29.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D207" s="8"/>
       <c r="F207" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K207" s="11"/>
     </row>
@@ -12490,52 +12496,52 @@
         <v>59</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D208" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K208" s="11"/>
     </row>
     <row r="209" customFormat="false" ht="44.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D209" s="8"/>
       <c r="F209" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K209" s="11"/>
     </row>
     <row r="210" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D210" s="8"/>
       <c r="F210" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K210" s="11"/>
     </row>
     <row r="211" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D211" s="8"/>
       <c r="F211" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K211" s="11"/>
     </row>
@@ -12544,22 +12550,22 @@
         <v>60</v>
       </c>
       <c r="B212" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D212" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K212" s="11"/>
     </row>
@@ -12568,10 +12574,10 @@
       <c r="C213" s="17"/>
       <c r="D213" s="8"/>
       <c r="F213" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K213" s="11"/>
     </row>
@@ -12580,10 +12586,10 @@
       <c r="C214" s="17"/>
       <c r="D214" s="8"/>
       <c r="F214" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K214" s="11"/>
     </row>
@@ -12592,10 +12598,10 @@
       <c r="C215" s="17"/>
       <c r="D215" s="8"/>
       <c r="F215" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K215" s="11"/>
     </row>
@@ -12604,68 +12610,68 @@
         <v>61</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D216" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K216" s="11"/>
     </row>
     <row r="217" customFormat="false" ht="36.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D217" s="8"/>
       <c r="F217" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="33.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D218" s="8"/>
       <c r="F218" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="44.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D219" s="8"/>
       <c r="F219" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K219" s="11"/>
     </row>
     <row r="220" customFormat="false" ht="28.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D220" s="8"/>
       <c r="F220" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K220" s="11"/>
     </row>
     <row r="221" customFormat="false" ht="14.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -12683,22 +12689,22 @@
         <v>62</v>
       </c>
       <c r="B222" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C222" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K222" s="11"/>
     </row>
@@ -12707,19 +12713,19 @@
         <v>63</v>
       </c>
       <c r="B223" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C223" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D223" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>27</v>
@@ -12731,22 +12737,22 @@
         <v>64</v>
       </c>
       <c r="B224" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C224" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D224" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I224" s="1"/>
       <c r="K224" s="11"/>
@@ -12756,10 +12762,10 @@
       <c r="C225" s="17"/>
       <c r="D225" s="8"/>
       <c r="F225" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
@@ -12770,22 +12776,22 @@
         <v>65</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C226" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K226" s="11"/>
     </row>
@@ -12794,10 +12800,10 @@
       <c r="C227" s="17"/>
       <c r="D227" s="8"/>
       <c r="F227" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K227" s="11"/>
     </row>
@@ -12806,10 +12812,10 @@
       <c r="C228" s="17"/>
       <c r="D228" s="8"/>
       <c r="F228" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K228" s="11"/>
     </row>
@@ -12818,22 +12824,22 @@
         <v>66</v>
       </c>
       <c r="B229" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C229" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D229" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K229" s="11"/>
     </row>
@@ -12842,10 +12848,10 @@
       <c r="C230" s="17"/>
       <c r="D230" s="8"/>
       <c r="F230" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K230" s="11"/>
     </row>
@@ -12854,10 +12860,10 @@
       <c r="C231" s="17"/>
       <c r="D231" s="8"/>
       <c r="F231" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K231" s="11"/>
     </row>
@@ -12866,10 +12872,10 @@
       <c r="C232" s="17"/>
       <c r="D232" s="8"/>
       <c r="F232" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K232" s="11"/>
     </row>
@@ -12878,28 +12884,28 @@
         <v>67</v>
       </c>
       <c r="B233" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C233" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D233" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I233" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K233" s="11"/>
     </row>
@@ -12908,10 +12914,10 @@
       <c r="C234" s="17"/>
       <c r="D234" s="8"/>
       <c r="F234" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I234" s="16"/>
       <c r="J234" s="16"/>
@@ -12922,10 +12928,10 @@
       <c r="C235" s="17"/>
       <c r="D235" s="8"/>
       <c r="F235" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I235" s="16"/>
       <c r="J235" s="16"/>
@@ -12936,10 +12942,10 @@
       <c r="C236" s="17"/>
       <c r="D236" s="8"/>
       <c r="F236" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I236" s="16"/>
       <c r="J236" s="16"/>
@@ -12950,22 +12956,22 @@
         <v>68</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C237" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D237" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K237" s="11"/>
     </row>
@@ -12974,10 +12980,10 @@
       <c r="C238" s="17"/>
       <c r="D238" s="8"/>
       <c r="F238" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K238" s="11"/>
     </row>
@@ -12986,22 +12992,22 @@
         <v>69</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C239" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D239" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K239" s="11"/>
     </row>
@@ -13010,10 +13016,10 @@
       <c r="C240" s="17"/>
       <c r="D240" s="8"/>
       <c r="F240" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K240" s="11"/>
     </row>
@@ -13022,22 +13028,22 @@
         <v>70</v>
       </c>
       <c r="B241" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C241" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D241" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K241" s="11"/>
     </row>
@@ -13046,10 +13052,10 @@
       <c r="C242" s="17"/>
       <c r="D242" s="8"/>
       <c r="F242" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K242" s="11"/>
     </row>
@@ -13058,22 +13064,22 @@
         <v>71</v>
       </c>
       <c r="B243" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C243" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D243" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K243" s="11"/>
     </row>
@@ -13082,10 +13088,10 @@
       <c r="C244" s="17"/>
       <c r="D244" s="8"/>
       <c r="F244" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K244" s="11"/>
     </row>
@@ -13094,10 +13100,10 @@
       <c r="C245" s="17"/>
       <c r="D245" s="8"/>
       <c r="F245" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K245" s="11"/>
     </row>
@@ -13106,22 +13112,22 @@
         <v>72</v>
       </c>
       <c r="B246" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C246" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D246" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K246" s="11"/>
     </row>
@@ -13130,10 +13136,10 @@
       <c r="C247" s="17"/>
       <c r="D247" s="8"/>
       <c r="F247" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K247" s="11"/>
     </row>
@@ -13142,10 +13148,10 @@
       <c r="C248" s="17"/>
       <c r="D248" s="8"/>
       <c r="F248" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K248" s="11"/>
     </row>
@@ -13154,10 +13160,10 @@
       <c r="C249" s="17"/>
       <c r="D249" s="8"/>
       <c r="F249" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K249" s="11"/>
     </row>
@@ -13166,10 +13172,10 @@
       <c r="C250" s="17"/>
       <c r="D250" s="8"/>
       <c r="F250" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K250" s="11"/>
     </row>
@@ -13178,22 +13184,22 @@
         <v>73</v>
       </c>
       <c r="B251" s="17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C251" s="17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K251" s="11"/>
     </row>
@@ -13202,10 +13208,10 @@
       <c r="C252" s="17"/>
       <c r="D252" s="8"/>
       <c r="F252" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K252" s="11"/>
     </row>
@@ -13214,10 +13220,10 @@
       <c r="C253" s="17"/>
       <c r="D253" s="8"/>
       <c r="F253" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K253" s="11"/>
     </row>
@@ -13226,22 +13232,22 @@
         <v>74</v>
       </c>
       <c r="B254" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C254" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D254" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K254" s="11"/>
     </row>
@@ -13250,10 +13256,10 @@
       <c r="C255" s="17"/>
       <c r="D255" s="8"/>
       <c r="F255" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K255" s="11"/>
     </row>
@@ -13262,10 +13268,10 @@
       <c r="C256" s="17"/>
       <c r="D256" s="8"/>
       <c r="F256" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K256" s="11"/>
     </row>
@@ -13274,22 +13280,22 @@
         <v>75</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C257" s="17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D257" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K257" s="11"/>
     </row>
@@ -13298,10 +13304,10 @@
       <c r="C258" s="17"/>
       <c r="D258" s="8"/>
       <c r="F258" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K258" s="11"/>
     </row>
@@ -13310,10 +13316,10 @@
       <c r="C259" s="17"/>
       <c r="D259" s="8"/>
       <c r="F259" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K259" s="11"/>
     </row>
@@ -13322,25 +13328,25 @@
         <v>76</v>
       </c>
       <c r="B260" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C260" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K260" s="11"/>
     </row>
@@ -13349,10 +13355,10 @@
       <c r="C261" s="17"/>
       <c r="D261" s="8"/>
       <c r="F261" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K261" s="11"/>
     </row>
@@ -13361,10 +13367,10 @@
       <c r="C262" s="17"/>
       <c r="D262" s="8"/>
       <c r="F262" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K262" s="11"/>
     </row>
@@ -13373,22 +13379,22 @@
         <v>77</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C263" s="17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D263" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K263" s="11"/>
     </row>
@@ -13397,10 +13403,10 @@
       <c r="C264" s="17"/>
       <c r="D264" s="8"/>
       <c r="F264" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K264" s="11"/>
     </row>
@@ -13409,10 +13415,10 @@
       <c r="C265" s="17"/>
       <c r="D265" s="8"/>
       <c r="F265" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K265" s="11"/>
     </row>
